--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF6238B4-8FB9-4718-8F85-9DE08650F12E}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AB7E3BF-C342-4904-A918-4D5E3796F640}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -19453,7 +19453,7 @@
         <v>299</v>
       </c>
       <c r="I121" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J121" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -19905,39 +19905,39 @@
       </c>
       <c r="J127" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K127" s="11">
         <v>2</v>
       </c>
       <c r="L127" s="18"/>
       <c r="M127" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>-0.15</v>
       </c>
       <c r="N127" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="O127" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>-0.15</v>
       </c>
       <c r="P127" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="Q127" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>-0.15</v>
       </c>
       <c r="R127" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="S127" s="18">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="T127" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="U127" s="18"/>
       <c r="V127" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="W127" s="19"/>
       <c r="X127" s="20"/>
@@ -19955,11 +19955,11 @@
       <c r="AJ127" s="20"/>
       <c r="AK127" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="AL127" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:38">
@@ -19990,11 +19990,11 @@
         <v>299</v>
       </c>
       <c r="I128" s="11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J128" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>3.5999999999999996</v>
+        <v>4</v>
       </c>
       <c r="K128" s="11"/>
       <c r="L128" s="18"/>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="T128" s="18"/>
       <c r="U128" s="19">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="V128" s="18"/>
       <c r="W128" s="19"/>
@@ -20030,11 +20030,11 @@
       <c r="AJ128" s="20"/>
       <c r="AK128" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="AL128" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>7.1999999999999993</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:38">
@@ -22228,7 +22228,7 @@
         <v>299</v>
       </c>
       <c r="I157" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J157" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -22305,7 +22305,7 @@
         <v>345</v>
       </c>
       <c r="I158" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J158" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="W49">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
+        <v>30.000000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:23">
@@ -34805,7 +34805,7 @@
       </c>
       <c r="W78">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
+        <v>30.000000000000004</v>
       </c>
     </row>
     <row r="79" spans="1:23">
@@ -37437,7 +37437,7 @@
       </c>
       <c r="C54">
         <f>SUMIF(Table1[Module Code],Sheet2!A54,Table1[Total Hours])</f>
-        <v>23.2</v>
+        <v>18</v>
       </c>
       <c r="D54">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A54,Table14[Module Code],0))</f>
@@ -37445,11 +37445,11 @@
       </c>
       <c r="E54">
         <f t="shared" si="0"/>
-        <v>56.2</v>
+        <v>51</v>
       </c>
       <c r="F54">
         <f t="shared" si="1"/>
-        <v>5.62</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="55" spans="1:6">

--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AB7E3BF-C342-4904-A918-4D5E3796F640}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D7AFE08-7DBE-4236-BC23-F2220BA50AEA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -12065,8 +12065,8 @@
       <c r="B25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>5</v>
+      <c r="C25" s="51" t="s">
+        <v>4</v>
       </c>
       <c r="D25" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -12076,8 +12076,8 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>206</v>
+      <c r="F25" s="51" t="s">
+        <v>267</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>229</v>
@@ -14560,19 +14560,19 @@
       <c r="B57" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="11" t="s">
-        <v>125</v>
+      <c r="C57" s="51" t="s">
+        <v>4</v>
       </c>
       <c r="D57" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E57" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F57" s="11" t="s">
-        <v>261</v>
+      <c r="F57" s="51" t="s">
+        <v>267</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>229</v>
@@ -14646,14 +14646,14 @@
       </c>
       <c r="D58" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E58" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>206</v>
+        <v>378</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>229</v>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="J58" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K58" s="11">
         <v>15</v>
@@ -14688,12 +14688,12 @@
       <c r="Z58" s="20"/>
       <c r="AA58" s="20"/>
       <c r="AB58" s="20">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AC58" s="20"/>
       <c r="AD58" s="20"/>
       <c r="AE58" s="20">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF58" s="20"/>
       <c r="AG58" s="20"/>
@@ -14702,11 +14702,11 @@
       <c r="AJ58" s="20"/>
       <c r="AK58" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AL58" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:38">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="D60" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E60" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -14818,7 +14818,7 @@
       </c>
       <c r="J60" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="K60" s="11"/>
       <c r="L60" s="18"/>
@@ -14835,19 +14835,19 @@
       <c r="W60" s="19"/>
       <c r="X60" s="20"/>
       <c r="Y60" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="Z60" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AA60" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AB60" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AC60" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AD60" s="20"/>
       <c r="AE60" s="20"/>
@@ -14858,11 +14858,11 @@
       <c r="AJ60" s="20"/>
       <c r="AK60" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="AL60" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:38" ht="28">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="D61" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E61" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="J61" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="18"/>
@@ -14919,29 +14919,29 @@
       <c r="AB61" s="20"/>
       <c r="AC61" s="20"/>
       <c r="AD61" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AE61" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AF61" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AG61" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AH61" s="20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AI61" s="20"/>
       <c r="AJ61" s="20"/>
       <c r="AK61" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="AL61" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:38">
@@ -31781,16 +31781,16 @@
       <c r="T21">
         <v>4</v>
       </c>
-      <c r="U21">
-        <v>70</v>
+      <c r="U21" s="48">
+        <v>80</v>
       </c>
       <c r="V21">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="W21">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30.000000000000004</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -31881,16 +31881,16 @@
       <c r="T23">
         <v>3</v>
       </c>
-      <c r="U23">
-        <v>70</v>
+      <c r="U23" s="48">
+        <v>80</v>
       </c>
       <c r="V23">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="W23">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="C22">
         <f>SUMIF(Table1[Module Code],Sheet2!A22,Table1[Total Hours])</f>
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A22,Table14[Module Code],0))</f>
@@ -36677,11 +36677,11 @@
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="F22">
         <f t="shared" si="1"/>
-        <v>3.95</v>
+        <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -36717,7 +36717,7 @@
       </c>
       <c r="C24">
         <f>SUMIF(Table1[Module Code],Sheet2!A24,Table1[Total Hours])</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A24,Table14[Module Code],0))</f>
@@ -36725,11 +36725,11 @@
       </c>
       <c r="E24">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F24">
         <f t="shared" si="1"/>
-        <v>4.5</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:6">

--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D7AFE08-7DBE-4236-BC23-F2220BA50AEA}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D36459A6-560D-4828-AB55-DDC0D9F28339}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="26115" windowHeight="15675" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="416">
   <si>
     <t>Module Code</t>
   </si>
@@ -1237,6 +1237,78 @@
   <si>
     <t>Quizzes
 (old)</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Astrophysics Project</t>
+  </si>
+  <si>
+    <t>Medical Physics Project</t>
+  </si>
+  <si>
+    <t>PX3360</t>
+  </si>
+  <si>
+    <t>PX3370</t>
+  </si>
+  <si>
+    <t>PX4320</t>
+  </si>
+  <si>
+    <t>C [6]</t>
+  </si>
+  <si>
+    <t>C [5]</t>
+  </si>
+  <si>
+    <t>O [1]</t>
+  </si>
+  <si>
+    <t>O [2]</t>
+  </si>
+  <si>
+    <t>O [3]</t>
+  </si>
+  <si>
+    <t>O [4]</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>PX2141 is strongly encouraged for students on placement degrees</t>
+  </si>
+  <si>
+    <t>[2]</t>
+  </si>
+  <si>
+    <t>Physics with Astronomy students should select exactly one of PX2241 and PX2242</t>
+  </si>
+  <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>Physics students should select **AT MOST** one astrophysics module per semester</t>
+  </si>
+  <si>
+    <t>[4]</t>
+  </si>
+  <si>
+    <t>Astrophysics students should select **AT LEAST** one astrophysics module per semester</t>
+  </si>
+  <si>
+    <t>[5]</t>
+  </si>
+  <si>
+    <t>A different module code exists for students on Astrophyscs (PX3360) and Medical Physics (PX3370) programmes</t>
+  </si>
+  <si>
+    <t>[6]</t>
+  </si>
+  <si>
+    <t>Astrophysics students take PX4320</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1469,9 +1541,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
@@ -1491,11 +1560,173 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="113">
+  <dxfs count="128">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1618,6 +1849,25 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
@@ -1698,25 +1948,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9644,54 +9875,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL188" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL188" totalsRowShown="0" headerRowDxfId="127" dataDxfId="125" headerRowBorderDxfId="126" tableBorderDxfId="124" totalsRowBorderDxfId="123">
   <autoFilter ref="A1:AL188" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI159">
     <sortCondition ref="A1:A159"/>
   </sortState>
   <tableColumns count="38">
-    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="107"/>
-    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="106"/>
-    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="105"/>
-    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="104"/>
-    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="103"/>
-    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="102"/>
-    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="101"/>
-    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="100"/>
-    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="99"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="98">
+    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="121"/>
+    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="120"/>
+    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="119"/>
+    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="118"/>
+    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="117"/>
+    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="116"/>
+    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="115"/>
+    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="114"/>
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="113">
       <calculatedColumnFormula>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="95"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="94"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="93"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="92"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="91"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="90"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="89"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="87"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="86"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="82"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="81"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="80"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="77"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="76"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="75"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="74"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="73"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="72"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="71">
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="112"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="111"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="110"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="109"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="108"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="107"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="106"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="105"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="104"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="103"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="102"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="101"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="100"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="99"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="98"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="97"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="96"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="95"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="94"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="93"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="92"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="91"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="90"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="89"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="88"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="87"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="86">
       <calculatedColumnFormula>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="70">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="85">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9700,49 +9931,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="62"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="77"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="76">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="60">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="75">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="59">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="74">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="49"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="47"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="46"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="45"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="44"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="43"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="42"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="41"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="40"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="39"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="38"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="37"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="36"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="35"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="67"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="66"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="65"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="64"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="63"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="62"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="61"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="60"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="59"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="58"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="57"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="56"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="55"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="54"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="53"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="52"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="51"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="50"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="49">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9751,37 +9982,38 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:W100" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32">
-  <autoFilter ref="A1:W100" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B62">
-    <sortCondition ref="A1:A62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:X109" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47">
+  <autoFilter ref="A1:X109" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B64">
+    <sortCondition ref="A1:A64"/>
   </sortState>
-  <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="22"/>
+  <tableColumns count="24">
+    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{BB8B1D0C-7F1D-4DB4-BBCE-55FD0E53BFE2}" name="Parent" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="38"/>
     <tableColumn id="17" xr3:uid="{AA3AE96F-2651-49D7-89AD-BA94806438AE}" name="PhysAstro"/>
-    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="36"/>
     <tableColumn id="20" xr3:uid="{C3673B06-C0A2-44F6-8978-F392282CECF8}" name="AllPG"/>
-    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="18"/>
-    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="17"/>
-    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="35"/>
+    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="34"/>
+    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="33"/>
+    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="32"/>
     <tableColumn id="18" xr3:uid="{10668F71-1EDF-482E-86A5-46E1F3C15120}" name="MScCSPhysics"/>
     <tableColumn id="23" xr3:uid="{E837FCBC-49C7-45CE-AFAA-4F01143EF2A8}" name="CDTCSPhysics"/>
     <tableColumn id="16" xr3:uid="{DB790F5F-BEF0-41CE-A68A-1AA9DF83D66B}" name="Contact Time"/>
-    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="14">
+    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="31"/>
+    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="30">
       <calculatedColumnFormula>100-Table2[[#This Row],[Exam Weight (%)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="13">
+    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="29">
       <calculatedColumnFormula>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10107,21 +10339,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66039B40-29AD-4D93-B125-EAF72A7B3996}">
   <dimension ref="A1:AL188"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.796875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="21.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.7265625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7265625" style="10" customWidth="1"/>
-    <col min="12" max="23" width="9.1796875" style="14" customWidth="1"/>
-    <col min="24" max="36" width="9.1796875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="21.73046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.73046875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="10.73046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.73046875" style="10" customWidth="1"/>
+    <col min="12" max="23" width="9.19921875" style="14" customWidth="1"/>
+    <col min="24" max="36" width="9.19921875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="44" customFormat="1" ht="29">
+    <row r="1" spans="1:38" s="44" customFormat="1" ht="28.5">
       <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
@@ -10535,7 +10767,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="28">
+    <row r="6" spans="1:38" ht="27">
       <c r="A6" s="4" t="s">
         <v>252</v>
       </c>
@@ -11116,7 +11348,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="28">
+    <row r="13" spans="1:38" ht="27">
       <c r="A13" s="3" t="s">
         <v>81</v>
       </c>
@@ -11892,7 +12124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="28">
+    <row r="23" spans="1:38" ht="27">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
@@ -12065,7 +12297,7 @@
       <c r="B25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="50" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="29">
@@ -12076,7 +12308,7 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F25" s="51" t="s">
+      <c r="F25" s="50" t="s">
         <v>267</v>
       </c>
       <c r="G25" s="11" t="s">
@@ -12686,40 +12918,40 @@
       </c>
     </row>
     <row r="33" spans="1:38">
-      <c r="A33" s="49" t="s">
+      <c r="A33" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="50" t="s">
+      <c r="B33" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="52">
+      <c r="D33" s="51">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="E33" s="52">
+      <c r="E33" s="51">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F33" s="51" t="s">
+      <c r="F33" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="51" t="s">
+      <c r="G33" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="H33" s="51" t="s">
+      <c r="H33" s="50" t="s">
         <v>305</v>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="50">
         <v>3</v>
       </c>
-      <c r="J33" s="51">
+      <c r="J33" s="50">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
-      <c r="K33" s="51">
+      <c r="K33" s="50">
         <v>6</v>
       </c>
       <c r="L33" s="18"/>
@@ -12758,7 +12990,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:38" ht="28">
+    <row r="34" spans="1:38" ht="27">
       <c r="A34" s="4" t="s">
         <v>44</v>
       </c>
@@ -13295,7 +13527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:38" ht="28">
+    <row r="41" spans="1:38" ht="27">
       <c r="A41" s="4" t="s">
         <v>49</v>
       </c>
@@ -14410,40 +14642,40 @@
       </c>
     </row>
     <row r="55" spans="1:38">
-      <c r="A55" s="49" t="s">
+      <c r="A55" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="50" t="s">
+      <c r="B55" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="C55" s="51" t="s">
+      <c r="C55" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="52">
+      <c r="D55" s="51">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E55" s="52">
+      <c r="E55" s="51">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F55" s="51" t="s">
+      <c r="F55" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="G55" s="51" t="s">
+      <c r="G55" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="H55" s="51" t="s">
+      <c r="H55" s="50" t="s">
         <v>299</v>
       </c>
-      <c r="I55" s="51">
+      <c r="I55" s="50">
         <v>10</v>
       </c>
-      <c r="J55" s="51">
+      <c r="J55" s="50">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
-      <c r="K55" s="51">
+      <c r="K55" s="50">
         <v>0.5</v>
       </c>
       <c r="L55" s="18"/>
@@ -14473,11 +14705,11 @@
       </c>
       <c r="AI55" s="20"/>
       <c r="AJ55" s="20"/>
-      <c r="AK55" s="47">
+      <c r="AK55" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
-      <c r="AL55" s="47">
+      <c r="AL55" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0.5</v>
       </c>
@@ -14560,7 +14792,7 @@
       <c r="B57" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="51" t="s">
+      <c r="C57" s="50" t="s">
         <v>4</v>
       </c>
       <c r="D57" s="29">
@@ -14571,7 +14803,7 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F57" s="51" t="s">
+      <c r="F57" s="50" t="s">
         <v>267</v>
       </c>
       <c r="G57" s="11" t="s">
@@ -14786,7 +15018,7 @@
         <v>12.000000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:38" ht="28">
+    <row r="60" spans="1:38" ht="27">
       <c r="A60" s="3" t="s">
         <v>186</v>
       </c>
@@ -14865,7 +15097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:38" ht="28">
+    <row r="61" spans="1:38" ht="27">
       <c r="A61" s="3" t="s">
         <v>186</v>
       </c>
@@ -15779,7 +16011,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="73" spans="1:38" ht="28">
+    <row r="73" spans="1:38" ht="27">
       <c r="A73" s="4" t="s">
         <v>1</v>
       </c>
@@ -15923,7 +16155,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:38" ht="28">
+    <row r="75" spans="1:38" ht="27">
       <c r="A75" s="4" t="s">
         <v>248</v>
       </c>
@@ -17079,7 +17311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:38" ht="28">
+    <row r="90" spans="1:38" ht="27">
       <c r="A90" s="4" t="s">
         <v>16</v>
       </c>
@@ -17243,7 +17475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:38" ht="28">
+    <row r="92" spans="1:38" ht="27">
       <c r="A92" s="4" t="s">
         <v>18</v>
       </c>
@@ -17322,7 +17554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" ht="28">
+    <row r="93" spans="1:38" ht="27">
       <c r="A93" s="4" t="s">
         <v>18</v>
       </c>
@@ -17995,7 +18227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:38" ht="28">
+    <row r="102" spans="1:38" ht="27">
       <c r="A102" s="3" t="s">
         <v>106</v>
       </c>
@@ -18285,7 +18517,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="106" spans="1:38" ht="28">
+    <row r="106" spans="1:38" ht="27">
       <c r="A106" s="3" t="s">
         <v>108</v>
       </c>
@@ -18430,40 +18662,40 @@
       </c>
     </row>
     <row r="108" spans="1:38">
-      <c r="A108" s="53" t="s">
+      <c r="A108" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="B108" s="53" t="s">
+      <c r="B108" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="C108" s="54" t="s">
+      <c r="C108" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="D108" s="52">
+      <c r="D108" s="51">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="E108" s="52">
+      <c r="E108" s="51">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F108" s="54" t="s">
+      <c r="F108" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="G108" s="51" t="s">
+      <c r="G108" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="H108" s="51" t="s">
+      <c r="H108" s="50" t="s">
         <v>299</v>
       </c>
-      <c r="I108" s="51">
-        <v>2</v>
-      </c>
-      <c r="J108" s="51">
+      <c r="I108" s="50">
+        <v>2</v>
+      </c>
+      <c r="J108" s="50">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0</v>
       </c>
-      <c r="K108" s="51">
+      <c r="K108" s="50">
         <v>15</v>
       </c>
       <c r="L108" s="18"/>
@@ -19425,7 +19657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:38" ht="28">
+    <row r="121" spans="1:38" ht="27">
       <c r="A121" s="4" t="s">
         <v>61</v>
       </c>
@@ -19800,7 +20032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:38" ht="28">
+    <row r="126" spans="1:38" ht="27">
       <c r="A126" s="4" t="s">
         <v>63</v>
       </c>
@@ -19873,7 +20105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:38" ht="28">
+    <row r="127" spans="1:38" ht="27">
       <c r="A127" s="4" t="s">
         <v>66</v>
       </c>
@@ -20335,7 +20567,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:38" ht="28">
+    <row r="133" spans="1:38" ht="27">
       <c r="A133" s="4" t="s">
         <v>71</v>
       </c>
@@ -20645,7 +20877,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:38" ht="28">
+    <row r="137" spans="1:38" ht="27">
       <c r="A137" s="3" t="s">
         <v>192</v>
       </c>
@@ -20878,7 +21110,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:38" ht="28">
+    <row r="140" spans="1:38" ht="27">
       <c r="A140" s="3" t="s">
         <v>193</v>
       </c>
@@ -20959,7 +21191,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="141" spans="1:38" ht="28">
+    <row r="141" spans="1:38" ht="27">
       <c r="A141" s="3" t="s">
         <v>193</v>
       </c>
@@ -21255,7 +21487,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="145" spans="1:38" ht="28">
+    <row r="145" spans="1:38" ht="27">
       <c r="A145" s="3" t="s">
         <v>239</v>
       </c>
@@ -21423,7 +21655,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="1:38" ht="28">
+    <row r="147" spans="1:38" ht="27">
       <c r="A147" s="3" t="s">
         <v>116</v>
       </c>
@@ -21502,7 +21734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:38" ht="28">
+    <row r="148" spans="1:38" ht="27">
       <c r="A148" s="3" t="s">
         <v>116</v>
       </c>
@@ -24557,16 +24789,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0482654D-1732-43E5-85EC-021407B07CE5}">
   <dimension ref="A1:AE141"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.796875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" style="10" customWidth="1"/>
-    <col min="7" max="15" width="16.26953125" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="17.26953125" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="8.7265625" style="16"/>
+    <col min="6" max="6" width="10.73046875" style="10" customWidth="1"/>
+    <col min="7" max="15" width="16.265625" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="17.265625" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="30" width="8.73046875" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -30706,20 +30938,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D548CE7-BEAC-43FA-847F-FDE82E3A5926}">
-  <dimension ref="A1:W129"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:X132"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.81640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.796875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.73046875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.265625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
+    <col min="8" max="9" width="9" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -30742,55 +30974,58 @@
         <v>140</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="4" t="s">
         <v>55</v>
       </c>
@@ -30810,10 +31045,8 @@
       <c r="G2" s="2">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J2" t="s">
@@ -30825,22 +31058,25 @@
       <c r="L2" t="s">
         <v>143</v>
       </c>
-      <c r="T2">
+      <c r="M2" t="s">
+        <v>143</v>
+      </c>
+      <c r="U2">
         <v>4</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>60</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W2">
+      <c r="X2">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="4" t="s">
         <v>252</v>
       </c>
@@ -30860,10 +31096,8 @@
       <c r="G3" s="2">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J3" t="s">
@@ -30875,22 +31109,25 @@
       <c r="L3" t="s">
         <v>143</v>
       </c>
-      <c r="T3">
+      <c r="M3" t="s">
+        <v>143</v>
+      </c>
+      <c r="U3">
         <v>4</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>60</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="4" t="s">
         <v>255</v>
       </c>
@@ -30910,10 +31147,8 @@
       <c r="G4" s="2">
         <v>10</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J4" t="s">
@@ -30925,22 +31160,25 @@
       <c r="L4" t="s">
         <v>143</v>
       </c>
-      <c r="T4">
-        <v>2</v>
+      <c r="M4" t="s">
+        <v>143</v>
       </c>
       <c r="U4">
+        <v>2</v>
+      </c>
+      <c r="V4">
         <v>50</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="4" t="s">
         <v>59</v>
       </c>
@@ -30960,10 +31198,8 @@
       <c r="G5" s="2">
         <v>20</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J5" t="s">
@@ -30975,22 +31211,25 @@
       <c r="L5" t="s">
         <v>143</v>
       </c>
-      <c r="T5">
+      <c r="M5" t="s">
+        <v>143</v>
+      </c>
+      <c r="U5">
         <v>4</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>0</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="3" t="s">
         <v>81</v>
       </c>
@@ -31010,10 +31249,8 @@
       <c r="G6" s="2">
         <v>20</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J6" t="s">
@@ -31025,22 +31262,25 @@
       <c r="L6" t="s">
         <v>143</v>
       </c>
-      <c r="T6">
+      <c r="M6" t="s">
+        <v>143</v>
+      </c>
+      <c r="U6">
         <v>4</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>70</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="3" t="s">
         <v>187</v>
       </c>
@@ -31060,10 +31300,8 @@
       <c r="G7" s="2">
         <v>10</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J7" t="s">
@@ -31075,22 +31313,25 @@
       <c r="L7" t="s">
         <v>143</v>
       </c>
-      <c r="T7">
+      <c r="M7" t="s">
+        <v>143</v>
+      </c>
+      <c r="U7">
         <v>3</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>0</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="3" t="s">
         <v>83</v>
       </c>
@@ -31110,19 +31351,19 @@
       <c r="G8" s="2">
         <v>10</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>144</v>
-      </c>
-      <c r="J8" t="s">
-        <v>143</v>
       </c>
       <c r="K8" t="s">
         <v>143</v>
       </c>
-      <c r="L8" s="6"/>
+      <c r="L8" t="s">
+        <v>143</v>
+      </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -31130,22 +31371,23 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
-      <c r="T8" s="6">
-        <v>2</v>
-      </c>
-      <c r="U8">
+      <c r="T8" s="6"/>
+      <c r="U8" s="6">
+        <v>2</v>
+      </c>
+      <c r="V8">
         <v>70</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="3" t="s">
         <v>84</v>
       </c>
@@ -31165,10 +31407,8 @@
       <c r="G9" s="2">
         <v>10</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J9" t="s">
@@ -31180,22 +31420,25 @@
       <c r="L9" t="s">
         <v>143</v>
       </c>
-      <c r="T9">
-        <v>2</v>
+      <c r="M9" t="s">
+        <v>143</v>
       </c>
       <c r="U9">
+        <v>2</v>
+      </c>
+      <c r="V9">
         <v>60</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="7" t="s">
         <v>82</v>
       </c>
@@ -31215,33 +31458,34 @@
       <c r="G10" s="2">
         <v>10</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>144</v>
       </c>
-      <c r="J10" s="6"/>
       <c r="K10" s="6"/>
-      <c r="L10" t="s">
+      <c r="L10" s="6"/>
+      <c r="M10" t="s">
         <v>143</v>
       </c>
-      <c r="T10">
-        <v>2</v>
-      </c>
       <c r="U10">
+        <v>2</v>
+      </c>
+      <c r="V10">
         <v>80</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="3" t="s">
         <v>215</v>
       </c>
@@ -31261,37 +31505,38 @@
       <c r="G11" s="2">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I11" t="s">
-        <v>143</v>
-      </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" t="s">
         <v>143</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="T11">
+      <c r="M11" t="s">
+        <v>143</v>
+      </c>
+      <c r="U11">
         <v>1</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>0</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24">
       <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
@@ -31311,10 +31556,8 @@
       <c r="G12" s="2">
         <v>20</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J12" t="s">
@@ -31326,22 +31569,25 @@
       <c r="L12" t="s">
         <v>143</v>
       </c>
-      <c r="T12">
+      <c r="M12" t="s">
+        <v>143</v>
+      </c>
+      <c r="U12">
         <v>4</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>60</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="4" t="s">
         <v>258</v>
       </c>
@@ -31361,10 +31607,8 @@
       <c r="G13" s="2">
         <v>10</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J13" t="s">
@@ -31376,22 +31620,25 @@
       <c r="L13" t="s">
         <v>143</v>
       </c>
-      <c r="T13">
+      <c r="M13" t="s">
+        <v>143</v>
+      </c>
+      <c r="U13">
         <v>3</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>60</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
@@ -31412,28 +31659,29 @@
         <v>10</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="6"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
-      <c r="L14" t="s">
+      <c r="L14" s="6"/>
+      <c r="M14" t="s">
         <v>143</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>4</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>0</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="4" t="s">
         <v>234</v>
       </c>
@@ -31453,10 +31701,8 @@
       <c r="G15" s="2">
         <v>10</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J15" t="s">
@@ -31468,22 +31714,25 @@
       <c r="L15" t="s">
         <v>143</v>
       </c>
-      <c r="T15">
+      <c r="M15" t="s">
+        <v>143</v>
+      </c>
+      <c r="U15">
         <v>3</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>0</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
@@ -31503,19 +31752,19 @@
       <c r="G16" s="2">
         <v>10</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J16" t="s">
         <v>144</v>
       </c>
       <c r="K16" t="s">
+        <v>144</v>
+      </c>
+      <c r="L16" t="s">
         <v>143</v>
       </c>
-      <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
@@ -31523,22 +31772,23 @@
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
-      <c r="T16" s="6">
-        <v>2</v>
-      </c>
-      <c r="U16" s="48">
+      <c r="T16" s="6"/>
+      <c r="U16" s="6">
+        <v>2</v>
+      </c>
+      <c r="V16" s="47">
         <v>80</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24">
       <c r="A17" s="4" t="s">
         <v>44</v>
       </c>
@@ -31558,16 +31808,16 @@
       <c r="G17" s="2">
         <v>10</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I17" t="s">
-        <v>144</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K17" s="6"/>
+      <c r="J17" t="s">
+        <v>400</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>400</v>
+      </c>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
@@ -31576,22 +31826,23 @@
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
-      <c r="T17" s="6">
-        <v>2</v>
-      </c>
-      <c r="U17">
+      <c r="T17" s="6"/>
+      <c r="U17" s="6">
+        <v>2</v>
+      </c>
+      <c r="V17">
         <v>0</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
@@ -31611,35 +31862,36 @@
       <c r="G18" s="2">
         <v>10</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>144</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="K18" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K18" s="6"/>
-      <c r="L18" t="s">
+      <c r="L18" s="6"/>
+      <c r="M18" t="s">
         <v>143</v>
       </c>
-      <c r="T18">
-        <v>2</v>
-      </c>
       <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
         <v>65</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>35</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:24">
       <c r="A19" s="4" t="s">
         <v>51</v>
       </c>
@@ -31659,13 +31911,13 @@
       <c r="G19" s="2">
         <v>20</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>143</v>
       </c>
-      <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -31675,22 +31927,23 @@
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
-      <c r="T19" s="6">
+      <c r="T19" s="6"/>
+      <c r="U19" s="6">
         <v>4</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>0</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100.00000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24">
       <c r="A20" s="4" t="s">
         <v>53</v>
       </c>
@@ -31710,17 +31963,17 @@
       <c r="G20" s="2">
         <v>20</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="J20" t="s">
-        <v>143</v>
-      </c>
+      <c r="J20" s="6"/>
       <c r="K20" t="s">
         <v>143</v>
       </c>
-      <c r="L20" s="6"/>
+      <c r="L20" t="s">
+        <v>143</v>
+      </c>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -31728,22 +31981,23 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
-      <c r="T20" s="6">
+      <c r="T20" s="6"/>
+      <c r="U20" s="6">
         <v>3</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>0</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:24">
       <c r="A21" s="3" t="s">
         <v>93</v>
       </c>
@@ -31763,10 +32017,8 @@
       <c r="G21" s="2">
         <v>20</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J21" t="s">
@@ -31778,22 +32030,25 @@
       <c r="L21" t="s">
         <v>143</v>
       </c>
-      <c r="T21">
+      <c r="M21" t="s">
+        <v>143</v>
+      </c>
+      <c r="U21">
         <v>4</v>
       </c>
-      <c r="U21" s="48">
+      <c r="V21" s="47">
         <v>80</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:24">
       <c r="A22" s="3" t="s">
         <v>94</v>
       </c>
@@ -31813,10 +32068,8 @@
       <c r="G22" s="2">
         <v>10</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J22" t="s">
@@ -31828,22 +32081,25 @@
       <c r="L22" t="s">
         <v>143</v>
       </c>
-      <c r="T22">
-        <v>2</v>
+      <c r="M22" t="s">
+        <v>143</v>
       </c>
       <c r="U22">
+        <v>2</v>
+      </c>
+      <c r="V22">
         <v>70</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:24">
       <c r="A23" s="3" t="s">
         <v>186</v>
       </c>
@@ -31863,10 +32119,8 @@
       <c r="G23" s="2">
         <v>10</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J23" t="s">
@@ -31878,22 +32132,25 @@
       <c r="L23" t="s">
         <v>143</v>
       </c>
-      <c r="T23">
+      <c r="M23" t="s">
+        <v>143</v>
+      </c>
+      <c r="U23">
         <v>3</v>
       </c>
-      <c r="U23" s="48">
+      <c r="V23" s="47">
         <v>80</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:24">
       <c r="A24" s="3" t="s">
         <v>89</v>
       </c>
@@ -31913,31 +32170,32 @@
       <c r="G24" s="2">
         <v>10</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="6"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
-      <c r="L24" t="s">
+      <c r="L24" s="6"/>
+      <c r="M24" t="s">
         <v>143</v>
       </c>
-      <c r="T24">
-        <v>2</v>
-      </c>
       <c r="U24">
+        <v>2</v>
+      </c>
+      <c r="V24">
         <v>80</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:24">
       <c r="A25" s="3" t="s">
         <v>91</v>
       </c>
@@ -31957,35 +32215,36 @@
       <c r="G25" s="2">
         <v>10</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>143</v>
       </c>
-      <c r="J25" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K25" s="6"/>
-      <c r="L25" t="s">
+      <c r="K25" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" t="s">
         <v>143</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>3</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>0</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" s="3" t="s">
         <v>95</v>
       </c>
@@ -32005,17 +32264,17 @@
       <c r="G26" s="2">
         <v>10</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I26" s="6"/>
-      <c r="J26" t="s">
-        <v>144</v>
-      </c>
+      <c r="J26" s="6"/>
       <c r="K26" t="s">
+        <v>401</v>
+      </c>
+      <c r="L26" t="s">
         <v>143</v>
       </c>
-      <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -32023,22 +32282,23 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="6"/>
-      <c r="T26" s="6">
+      <c r="T26" s="6"/>
+      <c r="U26" s="6">
         <v>3</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>0</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:24">
       <c r="A27" s="4" t="s">
         <v>1</v>
       </c>
@@ -32058,10 +32318,8 @@
       <c r="G27" s="2">
         <v>20</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J27" t="s">
@@ -32073,22 +32331,25 @@
       <c r="L27" t="s">
         <v>143</v>
       </c>
-      <c r="T27">
+      <c r="M27" t="s">
+        <v>143</v>
+      </c>
+      <c r="U27">
         <v>4</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>80</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:24">
       <c r="A28" s="4" t="s">
         <v>248</v>
       </c>
@@ -32110,14 +32371,12 @@
       <c r="G28" s="2">
         <v>10</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>143</v>
-      </c>
-      <c r="J28" t="s">
-        <v>144</v>
       </c>
       <c r="K28" t="s">
         <v>144</v>
@@ -32125,22 +32384,25 @@
       <c r="L28" t="s">
         <v>144</v>
       </c>
-      <c r="T28">
+      <c r="M28" t="s">
+        <v>144</v>
+      </c>
+      <c r="U28">
         <v>3</v>
       </c>
-      <c r="U28" s="48">
+      <c r="V28" s="47">
         <v>80</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:24">
       <c r="A29" s="4" t="s">
         <v>8</v>
       </c>
@@ -32162,10 +32424,8 @@
       <c r="G29" s="2">
         <v>10</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J29" t="s">
@@ -32177,22 +32437,25 @@
       <c r="L29" t="s">
         <v>144</v>
       </c>
-      <c r="T29">
-        <v>2</v>
+      <c r="M29" t="s">
+        <v>144</v>
       </c>
       <c r="U29">
+        <v>2</v>
+      </c>
+      <c r="V29">
         <v>0</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" s="4" t="s">
         <v>10</v>
       </c>
@@ -32214,37 +32477,35 @@
       <c r="G30" s="2">
         <v>10</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K30" t="s">
         <v>144</v>
       </c>
-      <c r="J30" t="s">
-        <v>144</v>
-      </c>
-      <c r="K30" t="s">
-        <v>143</v>
-      </c>
       <c r="L30" t="s">
-        <v>144</v>
-      </c>
-      <c r="T30">
-        <v>2</v>
+        <v>403</v>
       </c>
       <c r="U30">
+        <v>2</v>
+      </c>
+      <c r="V30">
         <v>80</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="4" t="s">
         <v>14</v>
       </c>
@@ -32266,10 +32527,8 @@
       <c r="G31" s="2">
         <v>10</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J31" t="s">
@@ -32281,22 +32540,25 @@
       <c r="L31" t="s">
         <v>144</v>
       </c>
-      <c r="T31">
-        <v>2</v>
+      <c r="M31" t="s">
+        <v>144</v>
       </c>
       <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31">
         <v>0</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="4" t="s">
         <v>15</v>
       </c>
@@ -32318,42 +32580,43 @@
       <c r="G32" s="2">
         <v>10</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>144</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="K32" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="6"/>
+      <c r="M32" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M32" s="6"/>
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="6"/>
-      <c r="T32" s="6">
-        <v>2</v>
-      </c>
-      <c r="U32">
+      <c r="T32" s="6"/>
+      <c r="U32" s="6">
+        <v>2</v>
+      </c>
+      <c r="V32">
         <v>0</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:24">
       <c r="A33" s="4" t="s">
         <v>16</v>
       </c>
@@ -32375,17 +32638,19 @@
       <c r="G33" s="2">
         <v>10</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I33" s="6"/>
-      <c r="J33" t="s">
+      <c r="J33" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K33" t="s">
         <v>144</v>
       </c>
-      <c r="K33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L33" s="6"/>
+      <c r="L33" t="s">
+        <v>403</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -32393,22 +32658,23 @@
       <c r="Q33" s="6"/>
       <c r="R33" s="6"/>
       <c r="S33" s="6"/>
-      <c r="T33" s="6">
-        <v>2</v>
-      </c>
-      <c r="U33">
+      <c r="T33" s="6"/>
+      <c r="U33" s="6">
+        <v>2</v>
+      </c>
+      <c r="V33">
         <v>70</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:24">
       <c r="A34" s="4" t="s">
         <v>18</v>
       </c>
@@ -32430,13 +32696,11 @@
       <c r="G34" s="2">
         <v>10</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I34" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="6" t="s">
+      <c r="J34" t="s">
         <v>144</v>
       </c>
       <c r="K34" s="6" t="s">
@@ -32445,29 +32709,32 @@
       <c r="L34" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M34" s="6"/>
+      <c r="M34" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
-      <c r="T34" s="6">
-        <v>2</v>
-      </c>
-      <c r="U34" s="48">
+      <c r="T34" s="6"/>
+      <c r="U34" s="6">
+        <v>2</v>
+      </c>
+      <c r="V34" s="47">
         <v>80</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:24">
       <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
@@ -32489,13 +32756,11 @@
       <c r="G35" s="2">
         <v>10</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I35" t="s">
-        <v>144</v>
-      </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" t="s">
         <v>144</v>
       </c>
       <c r="K35" s="6" t="s">
@@ -32504,29 +32769,32 @@
       <c r="L35" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M35" s="6"/>
+      <c r="M35" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
       <c r="R35" s="6"/>
       <c r="S35" s="6"/>
-      <c r="T35" s="6">
+      <c r="T35" s="6"/>
+      <c r="U35" s="6">
         <v>3</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <v>0</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:24">
       <c r="A36" s="8" t="s">
         <v>21</v>
       </c>
@@ -32546,40 +32814,41 @@
       <c r="G36" s="2">
         <v>10</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="2"/>
+      <c r="I36" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>144</v>
       </c>
-      <c r="J36" s="6"/>
       <c r="K36" s="6"/>
-      <c r="L36" s="6" t="s">
+      <c r="L36" s="6"/>
+      <c r="M36" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M36" s="6"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="6"/>
-      <c r="T36" s="6">
-        <v>2</v>
-      </c>
-      <c r="U36">
+      <c r="T36" s="6"/>
+      <c r="U36" s="6">
+        <v>2</v>
+      </c>
+      <c r="V36">
         <v>80</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:24">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
@@ -32599,10 +32868,8 @@
       <c r="G37" s="2">
         <v>20</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J37" t="s">
@@ -32614,22 +32881,25 @@
       <c r="L37" t="s">
         <v>143</v>
       </c>
-      <c r="T37">
+      <c r="M37" t="s">
+        <v>144</v>
+      </c>
+      <c r="U37">
         <v>4</v>
       </c>
-      <c r="U37">
+      <c r="V37">
         <v>70</v>
       </c>
-      <c r="V37">
+      <c r="W37">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W37">
+      <c r="X37">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:24">
       <c r="A38" s="3" t="s">
         <v>188</v>
       </c>
@@ -32649,10 +32919,8 @@
       <c r="G38" s="2">
         <v>10</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="H38" s="2"/>
+      <c r="I38" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J38" t="s">
@@ -32661,25 +32929,25 @@
       <c r="K38" t="s">
         <v>144</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>144</v>
       </c>
-      <c r="T38">
-        <v>2</v>
-      </c>
       <c r="U38">
+        <v>2</v>
+      </c>
+      <c r="V38">
         <v>80</v>
       </c>
-      <c r="V38">
+      <c r="W38">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W38">
+      <c r="X38">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:24">
       <c r="A39" s="3" t="s">
         <v>108</v>
       </c>
@@ -32701,10 +32969,8 @@
       <c r="G39" s="46">
         <v>10</v>
       </c>
-      <c r="H39" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="H39" s="46"/>
+      <c r="I39" s="28" t="s">
         <v>144</v>
       </c>
       <c r="J39" t="s">
@@ -32713,25 +32979,22 @@
       <c r="K39" t="s">
         <v>144</v>
       </c>
-      <c r="L39" t="s">
-        <v>144</v>
-      </c>
-      <c r="T39">
-        <v>2</v>
-      </c>
       <c r="U39">
+        <v>2</v>
+      </c>
+      <c r="V39">
         <v>80</v>
       </c>
-      <c r="V39">
+      <c r="W39">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W39">
+      <c r="X39">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:24">
       <c r="A40" s="3" t="s">
         <v>189</v>
       </c>
@@ -32753,17 +33016,19 @@
       <c r="G40" s="2">
         <v>10</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="2"/>
+      <c r="I40" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K40" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="L40" s="6"/>
+      <c r="L40" t="s">
+        <v>403</v>
+      </c>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
@@ -32771,22 +33036,23 @@
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="6"/>
-      <c r="T40" s="6">
-        <v>2</v>
-      </c>
-      <c r="U40" s="48">
+      <c r="T40" s="6"/>
+      <c r="U40" s="6">
+        <v>2</v>
+      </c>
+      <c r="V40" s="47">
         <v>80</v>
       </c>
-      <c r="V40">
+      <c r="W40">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W40">
+      <c r="X40">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:24">
       <c r="A41" s="3" t="s">
         <v>109</v>
       </c>
@@ -32808,10 +33074,8 @@
       <c r="G41" s="2">
         <v>10</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J41" t="s">
@@ -32823,22 +33087,25 @@
       <c r="L41" t="s">
         <v>144</v>
       </c>
-      <c r="T41">
-        <v>2</v>
+      <c r="M41" t="s">
+        <v>144</v>
       </c>
       <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="V41">
         <v>0</v>
       </c>
-      <c r="V41">
+      <c r="W41">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W41">
+      <c r="X41">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:24">
       <c r="A42" s="3" t="s">
         <v>100</v>
       </c>
@@ -32860,19 +33127,19 @@
       <c r="G42" s="2">
         <v>10</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="2"/>
+      <c r="I42" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K42" t="s">
         <v>144</v>
       </c>
-      <c r="J42" t="s">
-        <v>144</v>
-      </c>
-      <c r="K42" t="s">
-        <v>143</v>
-      </c>
-      <c r="L42" s="6"/>
+      <c r="L42" t="s">
+        <v>403</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
@@ -32880,22 +33147,23 @@
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
-      <c r="T42" s="6">
-        <v>2</v>
-      </c>
-      <c r="U42">
+      <c r="T42" s="6"/>
+      <c r="U42" s="6">
+        <v>2</v>
+      </c>
+      <c r="V42">
         <v>80</v>
       </c>
-      <c r="V42">
+      <c r="W42">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W42">
+      <c r="X42">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:24">
       <c r="A43" s="3" t="s">
         <v>102</v>
       </c>
@@ -32915,42 +33183,43 @@
       <c r="G43" s="2">
         <v>10</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="2"/>
+      <c r="I43" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>144</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="K43" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6" t="s">
+      <c r="L43" s="6"/>
+      <c r="M43" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M43" s="6"/>
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
       <c r="R43" s="6"/>
       <c r="S43" s="6"/>
-      <c r="T43" s="6">
-        <v>2</v>
-      </c>
-      <c r="U43">
+      <c r="T43" s="6"/>
+      <c r="U43" s="6">
+        <v>2</v>
+      </c>
+      <c r="V43">
         <v>80</v>
       </c>
-      <c r="V43">
+      <c r="W43">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W43">
+      <c r="X43">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:24">
       <c r="A44" s="3" t="s">
         <v>104</v>
       </c>
@@ -32970,42 +33239,43 @@
       <c r="G44" s="2">
         <v>10</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="2"/>
+      <c r="I44" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>144</v>
       </c>
-      <c r="J44" s="6" t="s">
+      <c r="K44" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="6"/>
+      <c r="M44" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6"/>
-      <c r="T44" s="6">
-        <v>2</v>
-      </c>
-      <c r="U44">
+      <c r="T44" s="6"/>
+      <c r="U44" s="6">
+        <v>2</v>
+      </c>
+      <c r="V44">
         <v>80</v>
       </c>
-      <c r="V44">
+      <c r="W44">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W44">
+      <c r="X44">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:24">
       <c r="A45" s="9" t="s">
         <v>47</v>
       </c>
@@ -33025,11 +33295,9 @@
       <c r="G45" s="2">
         <v>30</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I45" t="s">
-        <v>143</v>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>399</v>
       </c>
       <c r="J45" t="s">
         <v>143</v>
@@ -33037,147 +33305,112 @@
       <c r="K45" t="s">
         <v>143</v>
       </c>
-      <c r="L45" t="s">
-        <v>143</v>
-      </c>
-      <c r="T45">
+      <c r="U45">
         <v>0.5</v>
       </c>
-      <c r="U45">
+      <c r="V45">
         <v>0</v>
       </c>
-      <c r="V45">
+      <c r="W45">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W45">
+      <c r="X45">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="4" t="s">
-        <v>61</v>
+    <row r="46" spans="1:24">
+      <c r="A46" s="54" t="s">
+        <v>395</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="C46" s="54"/>
       <c r="D46" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F46" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G46" s="2">
-        <v>10</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J46" t="s">
-        <v>144</v>
-      </c>
-      <c r="K46" t="s">
+        <v>30</v>
+      </c>
+      <c r="H46" s="56" t="s">
+        <v>395</v>
+      </c>
+      <c r="I46" s="28"/>
+      <c r="L46" t="s">
         <v>143</v>
       </c>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6">
-        <v>2</v>
-      </c>
-      <c r="U46">
-        <v>70</v>
-      </c>
-      <c r="V46">
+      <c r="O46" s="57"/>
+      <c r="P46" s="57"/>
+      <c r="Q46" s="57"/>
+      <c r="R46" s="57"/>
+      <c r="V46" s="57"/>
+      <c r="W46" s="58">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W46">
+        <v>100</v>
+      </c>
+      <c r="X46" s="58">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
-      <c r="A47" s="4" t="s">
-        <v>238</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24">
+      <c r="A47" s="54" t="s">
+        <v>396</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>251</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="C47" s="54"/>
       <c r="D47" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F47" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G47" s="2">
-        <v>10</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I47" t="s">
-        <v>144</v>
-      </c>
-      <c r="J47" t="s">
-        <v>144</v>
-      </c>
-      <c r="K47" t="s">
-        <v>144</v>
-      </c>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-      <c r="T47" s="6">
-        <v>2</v>
-      </c>
-      <c r="U47">
-        <v>70</v>
-      </c>
-      <c r="V47">
+        <v>30</v>
+      </c>
+      <c r="H47" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" s="28"/>
+      <c r="M47" t="s">
+        <v>143</v>
+      </c>
+      <c r="O47" s="57"/>
+      <c r="P47" s="57"/>
+      <c r="Q47" s="57"/>
+      <c r="R47" s="57"/>
+      <c r="V47" s="57"/>
+      <c r="W47" s="58">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W47">
+        <v>100</v>
+      </c>
+      <c r="X47" s="58">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24">
       <c r="A48" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>293</v>
+        <v>62</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>180</v>
@@ -33191,15 +33424,19 @@
       <c r="G48" s="2">
         <v>10</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>144</v>
       </c>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
+      <c r="K48" t="s">
+        <v>144</v>
+      </c>
+      <c r="L48" t="s">
+        <v>143</v>
+      </c>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
@@ -33207,30 +33444,31 @@
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
-      <c r="T48" s="6">
-        <v>2</v>
-      </c>
-      <c r="U48">
-        <v>75</v>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6">
+        <v>2</v>
       </c>
       <c r="V48">
+        <v>70</v>
+      </c>
+      <c r="W48">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>25</v>
-      </c>
-      <c r="W48">
+        <v>30</v>
+      </c>
+      <c r="X48">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24">
       <c r="A49" s="4" t="s">
-        <v>66</v>
+        <v>238</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>180</v>
@@ -33244,10 +33482,8 @@
       <c r="G49" s="2">
         <v>10</v>
       </c>
-      <c r="H49" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J49" t="s">
@@ -33256,7 +33492,9 @@
       <c r="K49" t="s">
         <v>144</v>
       </c>
-      <c r="L49" s="6"/>
+      <c r="L49" t="s">
+        <v>144</v>
+      </c>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
@@ -33264,30 +33502,31 @@
       <c r="Q49" s="6"/>
       <c r="R49" s="6"/>
       <c r="S49" s="6"/>
-      <c r="T49" s="6">
-        <v>3</v>
-      </c>
-      <c r="U49">
+      <c r="T49" s="6"/>
+      <c r="U49" s="6">
+        <v>2</v>
+      </c>
+      <c r="V49">
         <v>70</v>
       </c>
-      <c r="V49">
+      <c r="W49">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W49">
+      <c r="X49">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30.000000000000004</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24">
       <c r="A50" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>70</v>
+        <v>293</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>180</v>
@@ -33301,18 +33540,14 @@
       <c r="G50" s="2">
         <v>10</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="H50" s="2"/>
+      <c r="I50" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J50" t="s">
         <v>144</v>
       </c>
-      <c r="K50" t="s">
-        <v>144</v>
-      </c>
+      <c r="K50" s="6"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
@@ -33321,30 +33556,31 @@
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
       <c r="S50" s="6"/>
-      <c r="T50" s="6">
-        <v>2</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
+      <c r="T50" s="6"/>
+      <c r="U50" s="6">
+        <v>2</v>
       </c>
       <c r="V50">
+        <v>75</v>
+      </c>
+      <c r="W50">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W50">
+        <v>25</v>
+      </c>
+      <c r="X50">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24">
       <c r="A51" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>180</v>
@@ -33358,10 +33594,8 @@
       <c r="G51" s="2">
         <v>10</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="H51" s="2"/>
+      <c r="I51" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J51" t="s">
@@ -33370,7 +33604,9 @@
       <c r="K51" t="s">
         <v>144</v>
       </c>
-      <c r="L51" s="6"/>
+      <c r="L51" t="s">
+        <v>144</v>
+      </c>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
@@ -33378,36 +33614,37 @@
       <c r="Q51" s="6"/>
       <c r="R51" s="6"/>
       <c r="S51" s="6"/>
-      <c r="T51" s="6">
-        <v>2</v>
-      </c>
-      <c r="U51">
-        <v>50</v>
+      <c r="T51" s="6"/>
+      <c r="U51" s="6">
+        <v>3</v>
       </c>
       <c r="V51">
+        <v>70</v>
+      </c>
+      <c r="W51">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="W51">
+        <v>30</v>
+      </c>
+      <c r="X51">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23">
-      <c r="A52" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>154</v>
+        <v>30.000000000000004</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24">
+      <c r="A52" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>148</v>
+      <c r="E52" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F52" s="2">
         <v>7</v>
@@ -33415,15 +33652,19 @@
       <c r="G52" s="2">
         <v>10</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="2"/>
+      <c r="I52" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>144</v>
       </c>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="K52" t="s">
+        <v>144</v>
+      </c>
+      <c r="L52" t="s">
+        <v>144</v>
+      </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
@@ -33431,36 +33672,37 @@
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
-      <c r="T52" s="6">
-        <v>2</v>
-      </c>
-      <c r="U52">
-        <v>80</v>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6">
+        <v>2</v>
       </c>
       <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="W52">
+        <v>100</v>
+      </c>
+      <c r="X52">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23">
-      <c r="A53" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>153</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24">
+      <c r="A53" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>148</v>
+      <c r="E53" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F53" s="2">
         <v>7</v>
@@ -33468,10 +33710,8 @@
       <c r="G53" s="2">
         <v>10</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="H53" s="2"/>
+      <c r="I53" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J53" t="s">
@@ -33480,7 +33720,9 @@
       <c r="K53" t="s">
         <v>144</v>
       </c>
-      <c r="L53" s="6"/>
+      <c r="L53" t="s">
+        <v>144</v>
+      </c>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
@@ -33488,30 +33730,31 @@
       <c r="Q53" s="6"/>
       <c r="R53" s="6"/>
       <c r="S53" s="6"/>
-      <c r="T53" s="6">
-        <v>2</v>
-      </c>
-      <c r="U53">
-        <v>70</v>
+      <c r="T53" s="6"/>
+      <c r="U53" s="6">
+        <v>2</v>
       </c>
       <c r="V53">
+        <v>50</v>
+      </c>
+      <c r="W53">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W53">
+        <v>50</v>
+      </c>
+      <c r="X53">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24">
       <c r="A54" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>180</v>
@@ -33525,18 +33768,14 @@
       <c r="G54" s="2">
         <v>10</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I54" t="s">
+      <c r="H54" s="2"/>
+      <c r="I54" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J54" t="s">
         <v>144</v>
       </c>
-      <c r="K54" t="s">
-        <v>144</v>
-      </c>
+      <c r="K54" s="6"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
@@ -33545,30 +33784,31 @@
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
-      <c r="T54" s="6">
-        <v>2</v>
-      </c>
-      <c r="U54">
-        <v>40</v>
+      <c r="T54" s="6"/>
+      <c r="U54" s="6">
+        <v>2</v>
       </c>
       <c r="V54">
+        <v>80</v>
+      </c>
+      <c r="W54">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>60</v>
-      </c>
-      <c r="W54">
+        <v>20</v>
+      </c>
+      <c r="X54">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24">
       <c r="A55" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>180</v>
@@ -33582,17 +33822,19 @@
       <c r="G55" s="2">
         <v>10</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="2"/>
+      <c r="I55" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I55" s="6"/>
       <c r="J55" t="s">
         <v>144</v>
       </c>
       <c r="K55" t="s">
-        <v>143</v>
-      </c>
-      <c r="L55" s="6"/>
+        <v>144</v>
+      </c>
+      <c r="L55" t="s">
+        <v>144</v>
+      </c>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
       <c r="O55" s="6"/>
@@ -33600,30 +33842,31 @@
       <c r="Q55" s="6"/>
       <c r="R55" s="6"/>
       <c r="S55" s="6"/>
-      <c r="T55" s="6">
-        <v>2</v>
-      </c>
-      <c r="U55">
-        <v>80</v>
+      <c r="T55" s="6"/>
+      <c r="U55" s="6">
+        <v>2</v>
       </c>
       <c r="V55">
+        <v>70</v>
+      </c>
+      <c r="W55">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="W55">
+        <v>30</v>
+      </c>
+      <c r="X55">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24">
       <c r="A56" s="3" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>180</v>
@@ -33637,10 +33880,8 @@
       <c r="G56" s="2">
         <v>10</v>
       </c>
-      <c r="H56" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I56" t="s">
+      <c r="H56" s="2"/>
+      <c r="I56" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J56" t="s">
@@ -33649,7 +33890,9 @@
       <c r="K56" t="s">
         <v>144</v>
       </c>
-      <c r="L56" s="6"/>
+      <c r="L56" t="s">
+        <v>144</v>
+      </c>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
       <c r="O56" s="6"/>
@@ -33657,30 +33900,31 @@
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
-      <c r="T56" s="6">
-        <v>3</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6">
+        <v>2</v>
       </c>
       <c r="V56">
+        <v>40</v>
+      </c>
+      <c r="W56">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W56">
+        <v>60</v>
+      </c>
+      <c r="X56">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24">
       <c r="A57" s="3" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>180</v>
@@ -33694,19 +33938,17 @@
       <c r="G57" s="2">
         <v>10</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" s="2"/>
+      <c r="I57" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I57" t="s">
-        <v>144</v>
-      </c>
-      <c r="J57" t="s">
-        <v>144</v>
-      </c>
+      <c r="J57" s="6"/>
       <c r="K57" t="s">
         <v>144</v>
       </c>
-      <c r="L57" s="6"/>
+      <c r="L57" t="s">
+        <v>143</v>
+      </c>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
       <c r="O57" s="6"/>
@@ -33714,30 +33956,31 @@
       <c r="Q57" s="6"/>
       <c r="R57" s="6"/>
       <c r="S57" s="6"/>
-      <c r="T57" s="6">
-        <v>2</v>
-      </c>
-      <c r="U57">
-        <v>70</v>
+      <c r="T57" s="6"/>
+      <c r="U57" s="6">
+        <v>2</v>
       </c>
       <c r="V57">
+        <v>80</v>
+      </c>
+      <c r="W57">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W57">
+        <v>20</v>
+      </c>
+      <c r="X57">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24">
       <c r="A58" s="3" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>180</v>
@@ -33751,15 +33994,19 @@
       <c r="G58" s="2">
         <v>10</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="2"/>
+      <c r="I58" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>144</v>
       </c>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
+      <c r="K58" t="s">
+        <v>144</v>
+      </c>
+      <c r="L58" t="s">
+        <v>144</v>
+      </c>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
       <c r="O58" s="6"/>
@@ -33767,30 +34014,31 @@
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
       <c r="S58" s="6"/>
-      <c r="T58" s="6">
-        <v>2</v>
-      </c>
-      <c r="U58">
-        <v>50</v>
+      <c r="T58" s="6"/>
+      <c r="U58" s="6">
+        <v>3</v>
       </c>
       <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="W58">
+        <v>100</v>
+      </c>
+      <c r="X58">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24">
       <c r="A59" s="3" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>180</v>
@@ -33804,10 +34052,8 @@
       <c r="G59" s="2">
         <v>10</v>
       </c>
-      <c r="H59" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I59" t="s">
+      <c r="H59" s="2"/>
+      <c r="I59" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J59" t="s">
@@ -33816,7 +34062,9 @@
       <c r="K59" t="s">
         <v>144</v>
       </c>
-      <c r="L59" s="6"/>
+      <c r="L59" t="s">
+        <v>144</v>
+      </c>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
       <c r="O59" s="6"/>
@@ -33824,30 +34072,31 @@
       <c r="Q59" s="6"/>
       <c r="R59" s="6"/>
       <c r="S59" s="6"/>
-      <c r="T59" s="6">
-        <v>3</v>
-      </c>
-      <c r="U59">
-        <v>60</v>
+      <c r="T59" s="6"/>
+      <c r="U59" s="6">
+        <v>2</v>
       </c>
       <c r="V59">
+        <v>70</v>
+      </c>
+      <c r="W59">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>40</v>
-      </c>
-      <c r="W59">
+        <v>30</v>
+      </c>
+      <c r="X59">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24">
       <c r="A60" s="3" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>180</v>
@@ -33861,18 +34110,14 @@
       <c r="G60" s="2">
         <v>10</v>
       </c>
-      <c r="H60" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="H60" s="2"/>
+      <c r="I60" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J60" t="s">
         <v>144</v>
       </c>
-      <c r="K60" t="s">
-        <v>144</v>
-      </c>
+      <c r="K60" s="6"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
@@ -33881,47 +34126,46 @@
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
-      <c r="T60" s="6">
-        <v>2</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6">
+        <v>2</v>
       </c>
       <c r="V60">
+        <v>50</v>
+      </c>
+      <c r="W60">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W60">
+        <v>50</v>
+      </c>
+      <c r="X60">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24">
       <c r="A61" s="3" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>240</v>
+        <v>118</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D61" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="2">
         <v>7</v>
       </c>
-      <c r="G61" s="28">
+      <c r="G61" s="2">
         <v>10</v>
       </c>
-      <c r="H61" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="H61" s="2"/>
+      <c r="I61" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J61" t="s">
@@ -33930,7 +34174,9 @@
       <c r="K61" t="s">
         <v>144</v>
       </c>
-      <c r="L61" s="6"/>
+      <c r="L61" t="s">
+        <v>144</v>
+      </c>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
       <c r="O61" s="6"/>
@@ -33938,54 +34184,57 @@
       <c r="Q61" s="6"/>
       <c r="R61" s="6"/>
       <c r="S61" s="6"/>
-      <c r="T61" s="6">
-        <v>2</v>
-      </c>
-      <c r="U61">
-        <v>50</v>
+      <c r="T61" s="6"/>
+      <c r="U61" s="6">
+        <v>3</v>
       </c>
       <c r="V61">
+        <v>60</v>
+      </c>
+      <c r="W61">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="W61">
+        <v>40</v>
+      </c>
+      <c r="X61">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23">
-      <c r="A62" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24">
+      <c r="A62" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>162</v>
+      </c>
       <c r="D62" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>149</v>
+      <c r="E62" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="F62" s="2">
         <v>7</v>
       </c>
       <c r="G62" s="2">
-        <v>60</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I62" t="s">
-        <v>143</v>
+        <v>10</v>
+      </c>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="J62" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K62" t="s">
-        <v>143</v>
-      </c>
-      <c r="L62" s="6"/>
+        <v>144</v>
+      </c>
+      <c r="L62" t="s">
+        <v>144</v>
+      </c>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
       <c r="O62" s="6"/>
@@ -33993,1601 +34242,1649 @@
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
       <c r="S62" s="6"/>
-      <c r="T62" s="6">
+      <c r="T62" s="6"/>
+      <c r="U62" s="6">
+        <v>2</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X62">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24">
+      <c r="A63" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F63" s="4">
+        <v>7</v>
+      </c>
+      <c r="G63" s="28">
+        <v>10</v>
+      </c>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="J63" t="s">
+        <v>144</v>
+      </c>
+      <c r="K63" t="s">
+        <v>144</v>
+      </c>
+      <c r="L63" t="s">
+        <v>144</v>
+      </c>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="6"/>
+      <c r="T63" s="6"/>
+      <c r="U63" s="6">
+        <v>2</v>
+      </c>
+      <c r="V63">
+        <v>50</v>
+      </c>
+      <c r="W63">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>50</v>
+      </c>
+      <c r="X63">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24">
+      <c r="A64" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F64" s="2">
+        <v>7</v>
+      </c>
+      <c r="G64" s="2">
+        <v>60</v>
+      </c>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J64" t="s">
+        <v>143</v>
+      </c>
+      <c r="K64" t="s">
+        <v>143</v>
+      </c>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6">
         <v>0.5</v>
       </c>
-      <c r="U62">
+      <c r="V64">
         <v>25</v>
       </c>
-      <c r="V62">
+      <c r="W64">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>75</v>
       </c>
-      <c r="W62">
+      <c r="X64">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>75</v>
       </c>
     </row>
-    <row r="63" spans="1:23">
-      <c r="A63" s="3" t="s">
+    <row r="65" spans="1:24">
+      <c r="A65" s="54" t="s">
+        <v>397</v>
+      </c>
+      <c r="B65" s="54" t="s">
+        <v>393</v>
+      </c>
+      <c r="C65" s="54"/>
+      <c r="D65" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F65" s="2">
+        <v>7</v>
+      </c>
+      <c r="G65" s="2">
+        <v>60</v>
+      </c>
+      <c r="H65" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="I65" s="28"/>
+      <c r="L65" t="s">
+        <v>143</v>
+      </c>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="59"/>
+      <c r="P65" s="59"/>
+      <c r="Q65" s="59"/>
+      <c r="R65" s="59"/>
+      <c r="S65" s="6"/>
+      <c r="T65" s="6"/>
+      <c r="U65" s="6"/>
+      <c r="V65" s="57"/>
+      <c r="W65" s="58">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X65" s="58">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24">
+      <c r="A66" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="28" t="s">
+      <c r="D66" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F66" s="4">
         <v>7</v>
       </c>
-      <c r="G63" s="2">
+      <c r="G66" s="2">
         <v>10</v>
       </c>
-      <c r="H63" s="2"/>
-      <c r="M63" t="s">
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="N66" t="s">
         <v>144</v>
       </c>
-      <c r="N63" t="s">
+      <c r="O66" t="s">
         <v>144</v>
       </c>
-      <c r="T63">
-        <f>INDEX(T2:T62,MATCH(Table2[[#This Row],[Alternative Module Code]],A2:A62,0))</f>
+      <c r="U66">
+        <f>INDEX(U2:U64,MATCH(Table2[[#This Row],[Alternative Module Code]],A2:A64,0))</f>
         <v>3</v>
       </c>
-      <c r="U63">
+      <c r="V66">
         <v>70</v>
       </c>
-      <c r="V63">
+      <c r="W66">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W63">
+      <c r="X66">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
-      <c r="A64" s="3" t="s">
+    <row r="67" spans="1:24">
+      <c r="A67" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B67" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="D67" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F67" s="4">
         <v>7</v>
       </c>
-      <c r="G64" s="2">
+      <c r="G67" s="2">
         <v>10</v>
       </c>
-      <c r="H64" s="2"/>
-      <c r="M64" t="s">
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="N67" t="s">
         <v>144</v>
       </c>
-      <c r="N64" t="s">
+      <c r="O67" t="s">
         <v>144</v>
       </c>
-      <c r="O64" t="s">
+      <c r="P67" t="s">
         <v>144</v>
       </c>
-      <c r="R64" t="s">
+      <c r="S67" t="s">
         <v>144</v>
       </c>
-      <c r="T64">
-        <f>INDEX(T3:T63,MATCH(Table2[[#This Row],[Alternative Module Code]],A3:A63,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U64">
+      <c r="U67">
+        <f>INDEX(U3:U66,MATCH(Table2[[#This Row],[Alternative Module Code]],A3:A66,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V67">
         <v>0</v>
       </c>
-      <c r="V64">
+      <c r="W67">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W64">
+      <c r="X67">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
-      <c r="A65" s="3" t="s">
+    <row r="68" spans="1:24">
+      <c r="A68" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D68" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F68" s="4">
         <v>7</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G68" s="2">
         <v>10</v>
       </c>
-      <c r="H65" s="2"/>
-      <c r="M65" t="s">
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="N68" t="s">
         <v>144</v>
       </c>
-      <c r="O65" t="s">
+      <c r="P68" t="s">
         <v>144</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="R68" t="s">
         <v>144</v>
       </c>
-      <c r="T65">
-        <f>INDEX(T4:T64,MATCH(Table2[[#This Row],[Alternative Module Code]],A4:A64,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U65">
+      <c r="U68">
+        <f>INDEX(U4:U67,MATCH(Table2[[#This Row],[Alternative Module Code]],A4:A67,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V68">
         <v>80</v>
       </c>
-      <c r="V65">
+      <c r="W68">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W65">
+      <c r="X68">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
-      <c r="A66" s="3" t="s">
+    <row r="69" spans="1:24">
+      <c r="A69" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="D69" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F69" s="4">
         <v>7</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G69" s="2">
         <v>10</v>
       </c>
-      <c r="H66" s="2"/>
-      <c r="M66" t="s">
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="N69" t="s">
         <v>144</v>
       </c>
-      <c r="N66" t="s">
+      <c r="O69" t="s">
         <v>144</v>
       </c>
-      <c r="T66">
-        <f>INDEX(T5:T65,MATCH(Table2[[#This Row],[Alternative Module Code]],A5:A65,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U66">
+      <c r="U69">
+        <f>INDEX(U5:U68,MATCH(Table2[[#This Row],[Alternative Module Code]],A5:A68,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V69">
         <v>0</v>
       </c>
-      <c r="V66">
+      <c r="W69">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W66">
+      <c r="X69">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:23">
-      <c r="A67" s="3" t="s">
+    <row r="70" spans="1:24">
+      <c r="A70" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D67" s="28" t="s">
+      <c r="D70" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F70" s="4">
         <v>7</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G70" s="2">
         <v>10</v>
       </c>
-      <c r="H67" s="2"/>
-      <c r="M67" t="s">
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="N70" t="s">
         <v>144</v>
       </c>
-      <c r="N67" t="s">
+      <c r="O70" t="s">
         <v>144</v>
       </c>
-      <c r="T67">
-        <f>INDEX(T6:T66,MATCH(Table2[[#This Row],[Alternative Module Code]],A6:A66,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U67">
+      <c r="U70">
+        <f>INDEX(U6:U69,MATCH(Table2[[#This Row],[Alternative Module Code]],A6:A69,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V70">
         <v>0</v>
       </c>
-      <c r="V67">
+      <c r="W70">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W67">
+      <c r="X70">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
-      <c r="A68" s="3" t="s">
+    <row r="71" spans="1:24">
+      <c r="A71" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D71" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F71" s="4">
         <v>7</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G71" s="2">
         <v>10</v>
       </c>
-      <c r="H68" s="2"/>
-      <c r="M68" t="s">
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="N71" t="s">
         <v>144</v>
       </c>
-      <c r="O68" t="s">
+      <c r="P71" t="s">
         <v>144</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R71" t="s">
         <v>144</v>
       </c>
-      <c r="T68">
-        <f>INDEX(T7:T67,MATCH(Table2[[#This Row],[Alternative Module Code]],A7:A67,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U68">
+      <c r="U71">
+        <f>INDEX(U7:U70,MATCH(Table2[[#This Row],[Alternative Module Code]],A7:A70,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V71">
         <v>70</v>
       </c>
-      <c r="V68">
+      <c r="W71">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W68">
+      <c r="X71">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:23">
-      <c r="A69" s="3" t="s">
+    <row r="72" spans="1:24">
+      <c r="A72" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="D72" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F72" s="4">
         <v>7</v>
       </c>
-      <c r="G69" s="2">
+      <c r="G72" s="2">
         <v>10</v>
       </c>
-      <c r="H69" s="2"/>
-      <c r="M69" t="s">
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="N72" t="s">
         <v>144</v>
       </c>
-      <c r="N69" t="s">
+      <c r="O72" t="s">
         <v>144</v>
       </c>
-      <c r="O69" t="s">
+      <c r="P72" t="s">
         <v>144</v>
       </c>
-      <c r="P69" t="s">
+      <c r="Q72" t="s">
         <v>144</v>
       </c>
-      <c r="T69">
-        <f>INDEX(T8:T68,MATCH(Table2[[#This Row],[Alternative Module Code]],A8:A68,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U69">
+      <c r="U72">
+        <f>INDEX(U8:U71,MATCH(Table2[[#This Row],[Alternative Module Code]],A8:A71,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V72">
         <v>70</v>
       </c>
-      <c r="V69">
+      <c r="W72">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W69">
+      <c r="X72">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
-      <c r="A70" s="3" t="s">
+    <row r="73" spans="1:24">
+      <c r="A73" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D73" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F73" s="4">
         <v>7</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G73" s="2">
         <v>10</v>
       </c>
-      <c r="H70" s="2"/>
-      <c r="M70" t="s">
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="N73" t="s">
         <v>144</v>
       </c>
-      <c r="N70" t="s">
+      <c r="O73" t="s">
         <v>144</v>
       </c>
-      <c r="O70" t="s">
+      <c r="P73" t="s">
         <v>144</v>
       </c>
-      <c r="R70" t="s">
+      <c r="S73" t="s">
         <v>144</v>
       </c>
-      <c r="T70">
-        <f>INDEX(T9:T69,MATCH(Table2[[#This Row],[Alternative Module Code]],A9:A69,0))</f>
+      <c r="U73">
+        <f>INDEX(U9:U72,MATCH(Table2[[#This Row],[Alternative Module Code]],A9:A72,0))</f>
         <v>3</v>
       </c>
-      <c r="U70">
+      <c r="V73">
         <v>0</v>
       </c>
-      <c r="V70">
+      <c r="W73">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W70">
+      <c r="X73">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
-      <c r="A71" s="3" t="s">
+    <row r="74" spans="1:24">
+      <c r="A74" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D74" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F74" s="4">
         <v>7</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G74" s="2">
         <v>10</v>
       </c>
-      <c r="H71" s="2"/>
-      <c r="M71" t="s">
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="N74" t="s">
         <v>144</v>
       </c>
-      <c r="O71" t="s">
+      <c r="P74" t="s">
         <v>144</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="R74" t="s">
         <v>144</v>
       </c>
-      <c r="T71">
-        <f>INDEX(T10:T70,MATCH(Table2[[#This Row],[Alternative Module Code]],A10:A70,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U71">
+      <c r="U74">
+        <f>INDEX(U10:U73,MATCH(Table2[[#This Row],[Alternative Module Code]],A10:A73,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V74">
         <v>60</v>
       </c>
-      <c r="V71">
+      <c r="W74">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W71">
+      <c r="X74">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
-      <c r="A72" s="3" t="s">
+    <row r="75" spans="1:24">
+      <c r="A75" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B75" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D72" s="28" t="s">
+      <c r="D75" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E75" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F75" s="4">
         <v>7</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G75" s="2">
         <v>10</v>
       </c>
-      <c r="H72" s="2"/>
-      <c r="M72" t="s">
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="N75" t="s">
         <v>144</v>
       </c>
-      <c r="N72" t="s">
+      <c r="O75" t="s">
         <v>144</v>
       </c>
-      <c r="R72" t="s">
+      <c r="S75" t="s">
         <v>144</v>
       </c>
-      <c r="S72" t="s">
+      <c r="T75" t="s">
         <v>144</v>
       </c>
-      <c r="T72">
-        <f>INDEX(T13:T71,MATCH(Table2[[#This Row],[Alternative Module Code]],A13:A71,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U72">
+      <c r="U75">
+        <f>INDEX(U13:U74,MATCH(Table2[[#This Row],[Alternative Module Code]],A13:A74,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V75">
         <v>0</v>
       </c>
-      <c r="V72">
+      <c r="W75">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W72">
+      <c r="X75">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
-      <c r="A73" s="3" t="s">
+    <row r="76" spans="1:24">
+      <c r="A76" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B76" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D73" s="28" t="s">
+      <c r="D76" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F76" s="4">
         <v>7</v>
       </c>
-      <c r="G73" s="2">
+      <c r="G76" s="2">
         <v>10</v>
       </c>
-      <c r="H73" s="2"/>
-      <c r="M73" t="s">
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="N76" t="s">
         <v>144</v>
       </c>
-      <c r="O73" t="s">
+      <c r="P76" t="s">
         <v>144</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="R76" t="s">
         <v>144</v>
       </c>
-      <c r="T73">
-        <f>INDEX(T14:T72,MATCH(Table2[[#This Row],[Alternative Module Code]],A14:A72,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U73">
+      <c r="U76">
+        <f>INDEX(U14:U75,MATCH(Table2[[#This Row],[Alternative Module Code]],A14:A75,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V76">
         <v>80</v>
       </c>
-      <c r="V73">
+      <c r="W76">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W73">
+      <c r="X76">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:23">
-      <c r="A74" s="3" t="s">
+    <row r="77" spans="1:24">
+      <c r="A77" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B77" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D74" s="28" t="s">
+      <c r="D77" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E77" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F77" s="4">
         <v>7</v>
       </c>
-      <c r="G74" s="28">
+      <c r="G77" s="28">
         <v>10</v>
       </c>
-      <c r="H74" s="28"/>
-      <c r="M74" t="s">
+      <c r="H77" s="28"/>
+      <c r="I77" s="28"/>
+      <c r="N77" t="s">
         <v>144</v>
       </c>
-      <c r="N74" t="s">
+      <c r="O77" t="s">
         <v>144</v>
       </c>
-      <c r="O74" t="s">
+      <c r="P77" t="s">
         <v>144</v>
       </c>
-      <c r="P74" t="s">
+      <c r="Q77" t="s">
         <v>144</v>
       </c>
-      <c r="Q74" t="s">
+      <c r="R77" t="s">
         <v>144</v>
       </c>
-      <c r="R74" t="s">
+      <c r="S77" t="s">
         <v>144</v>
       </c>
-      <c r="S74" t="s">
+      <c r="T77" t="s">
         <v>144</v>
       </c>
-      <c r="T74">
-        <v>2</v>
-      </c>
-      <c r="U74">
+      <c r="U77">
+        <v>2</v>
+      </c>
+      <c r="V77">
         <v>80</v>
       </c>
-      <c r="V74">
+      <c r="W77">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W74">
+      <c r="X77">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:23">
-      <c r="A75" s="3" t="s">
+    <row r="78" spans="1:24">
+      <c r="A78" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B78" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D75" s="28" t="s">
+      <c r="D78" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F78" s="4">
         <v>7</v>
       </c>
-      <c r="G75" s="2">
+      <c r="G78" s="2">
         <v>10</v>
       </c>
-      <c r="H75" s="2"/>
-      <c r="M75" t="s">
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="N78" t="s">
         <v>144</v>
       </c>
-      <c r="N75" t="s">
+      <c r="O78" t="s">
         <v>144</v>
       </c>
-      <c r="O75" t="s">
+      <c r="P78" t="s">
         <v>144</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R78" t="s">
         <v>144</v>
       </c>
-      <c r="T75">
-        <f>INDEX(T16:T73,MATCH(Table2[[#This Row],[Alternative Module Code]],A16:A73,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U75">
+      <c r="U78">
+        <f>INDEX(U16:U76,MATCH(Table2[[#This Row],[Alternative Module Code]],A16:A76,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V78">
         <v>70</v>
       </c>
-      <c r="V75">
+      <c r="W78">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W75">
+      <c r="X78">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:23">
-      <c r="A76" s="3" t="s">
+    <row r="79" spans="1:24">
+      <c r="A79" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D76" s="28" t="s">
+      <c r="D79" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E79" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F79" s="4">
         <v>7</v>
       </c>
-      <c r="G76" s="2">
+      <c r="G79" s="2">
         <v>10</v>
       </c>
-      <c r="H76" s="2"/>
-      <c r="M76" t="s">
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="N79" t="s">
         <v>144</v>
       </c>
-      <c r="N76" t="s">
+      <c r="O79" t="s">
         <v>144</v>
       </c>
-      <c r="O76" t="s">
+      <c r="P79" t="s">
         <v>144</v>
       </c>
-      <c r="R76" t="s">
+      <c r="S79" t="s">
         <v>144</v>
       </c>
-      <c r="S76" t="s">
+      <c r="T79" t="s">
         <v>144</v>
       </c>
-      <c r="T76">
-        <f>INDEX(T17:T75,MATCH(Table2[[#This Row],[Alternative Module Code]],A17:A75,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U76">
+      <c r="U79">
+        <f>INDEX(U17:U78,MATCH(Table2[[#This Row],[Alternative Module Code]],A17:A78,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V79">
         <v>70</v>
       </c>
-      <c r="V76">
+      <c r="W79">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W76">
+      <c r="X79">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:23">
-      <c r="A77" s="3" t="s">
+    <row r="80" spans="1:24">
+      <c r="A80" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D77" s="28" t="s">
+      <c r="D80" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F80" s="4">
         <v>7</v>
       </c>
-      <c r="G77" s="2">
+      <c r="G80" s="2">
         <v>10</v>
       </c>
-      <c r="H77" s="2"/>
-      <c r="M77" t="s">
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="N80" t="s">
         <v>144</v>
       </c>
-      <c r="N77" t="s">
+      <c r="O80" t="s">
         <v>144</v>
       </c>
-      <c r="R77" t="s">
+      <c r="S80" t="s">
         <v>143</v>
       </c>
-      <c r="S77" t="s">
+      <c r="T80" t="s">
         <v>143</v>
       </c>
-      <c r="T77">
-        <f>INDEX(T18:T76,MATCH(Table2[[#This Row],[Alternative Module Code]],A18:A76,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U77">
+      <c r="U80">
+        <f>INDEX(U18:U79,MATCH(Table2[[#This Row],[Alternative Module Code]],A18:A79,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V80">
         <v>75</v>
       </c>
-      <c r="V77">
+      <c r="W80">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>25</v>
       </c>
-      <c r="W77">
+      <c r="X80">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:23">
-      <c r="A78" s="3" t="s">
+    <row r="81" spans="1:24">
+      <c r="A81" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B81" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D78" s="28" t="s">
+      <c r="D81" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E81" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F81" s="4">
         <v>7</v>
       </c>
-      <c r="G78" s="2">
+      <c r="G81" s="2">
         <v>10</v>
       </c>
-      <c r="H78" s="2"/>
-      <c r="M78" t="s">
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="N81" t="s">
         <v>144</v>
       </c>
-      <c r="N78" t="s">
+      <c r="O81" t="s">
         <v>144</v>
       </c>
-      <c r="P78" t="s">
+      <c r="Q81" t="s">
         <v>144</v>
       </c>
-      <c r="R78" t="s">
+      <c r="S81" t="s">
         <v>144</v>
       </c>
-      <c r="S78" t="s">
+      <c r="T81" t="s">
         <v>144</v>
       </c>
-      <c r="T78">
-        <f>INDEX(T20:T77,MATCH(Table2[[#This Row],[Alternative Module Code]],A20:A77,0))</f>
+      <c r="U81">
+        <f>INDEX(U20:U80,MATCH(Table2[[#This Row],[Alternative Module Code]],A20:A80,0))</f>
         <v>3</v>
       </c>
-      <c r="U78">
+      <c r="V81">
         <v>70</v>
       </c>
-      <c r="V78">
+      <c r="W81">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W78">
+      <c r="X81">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="79" spans="1:23">
-      <c r="A79" s="3" t="s">
+    <row r="82" spans="1:24">
+      <c r="A82" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D79" s="28" t="s">
+      <c r="D82" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F82" s="4">
         <v>7</v>
       </c>
-      <c r="G79" s="2">
+      <c r="G82" s="2">
         <v>10</v>
       </c>
-      <c r="H79" s="2"/>
-      <c r="M79" t="s">
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="N82" t="s">
         <v>144</v>
       </c>
-      <c r="N79" t="s">
+      <c r="O82" t="s">
         <v>144</v>
       </c>
-      <c r="O79" t="s">
+      <c r="P82" t="s">
         <v>144</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q82" t="s">
         <v>143</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="R82" t="s">
         <v>143</v>
       </c>
-      <c r="R79" t="s">
+      <c r="S82" t="s">
         <v>144</v>
       </c>
-      <c r="S79" t="s">
+      <c r="T82" t="s">
         <v>144</v>
       </c>
-      <c r="T79">
-        <f>INDEX(T21:T78,MATCH(Table2[[#This Row],[Alternative Module Code]],A21:A78,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U79">
+      <c r="U82">
+        <f>INDEX(U21:U81,MATCH(Table2[[#This Row],[Alternative Module Code]],A21:A81,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V82">
         <v>0</v>
       </c>
-      <c r="V79">
+      <c r="W82">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W79">
+      <c r="X82">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:23">
-      <c r="A80" s="3" t="s">
+    <row r="83" spans="1:24">
+      <c r="A83" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B83" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D80" s="28" t="s">
+      <c r="D83" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E83" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F83" s="4">
         <v>7</v>
       </c>
-      <c r="G80" s="2">
+      <c r="G83" s="2">
         <v>10</v>
       </c>
-      <c r="H80" s="2"/>
-      <c r="M80" t="s">
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="N83" t="s">
         <v>144</v>
       </c>
-      <c r="N80" t="s">
+      <c r="O83" t="s">
         <v>144</v>
       </c>
-      <c r="O80" t="s">
+      <c r="P83" t="s">
         <v>144</v>
       </c>
-      <c r="R80" t="s">
+      <c r="S83" t="s">
         <v>144</v>
       </c>
-      <c r="S80" t="s">
+      <c r="T83" t="s">
         <v>144</v>
       </c>
-      <c r="T80">
-        <f>INDEX(T22:T79,MATCH(Table2[[#This Row],[Alternative Module Code]],A22:A79,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U80">
+      <c r="U83">
+        <f>INDEX(U22:U82,MATCH(Table2[[#This Row],[Alternative Module Code]],A22:A82,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V83">
         <v>50</v>
       </c>
-      <c r="V80">
+      <c r="W83">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W80">
+      <c r="X83">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:23">
-      <c r="A81" s="3" t="s">
+    <row r="84" spans="1:24">
+      <c r="A84" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B84" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D81" s="28" t="s">
+      <c r="D84" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F84" s="4">
         <v>7</v>
       </c>
-      <c r="G81" s="2">
+      <c r="G84" s="2">
         <v>10</v>
       </c>
-      <c r="H81" s="2"/>
-      <c r="M81" t="s">
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="N84" t="s">
         <v>144</v>
       </c>
-      <c r="N81" t="s">
+      <c r="O84" t="s">
         <v>144</v>
       </c>
-      <c r="P81" t="s">
+      <c r="Q84" t="s">
         <v>144</v>
       </c>
-      <c r="R81" t="s">
+      <c r="S84" t="s">
         <v>144</v>
       </c>
-      <c r="S81" t="s">
+      <c r="T84" t="s">
         <v>144</v>
       </c>
-      <c r="T81">
-        <f>INDEX(T23:T80,MATCH(Table2[[#This Row],[Alternative Module Code]],A23:A80,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U81">
+      <c r="U84">
+        <f>INDEX(U23:U83,MATCH(Table2[[#This Row],[Alternative Module Code]],A23:A83,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V84">
         <v>80</v>
       </c>
-      <c r="V81">
+      <c r="W84">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W81">
+      <c r="X84">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:23">
-      <c r="A82" s="3" t="s">
+    <row r="85" spans="1:24">
+      <c r="A85" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B85" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D82" s="28" t="s">
+      <c r="D85" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F85" s="4">
         <v>7</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G85" s="2">
         <v>10</v>
       </c>
-      <c r="H82" s="2"/>
-      <c r="M82" t="s">
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="N85" t="s">
         <v>144</v>
       </c>
-      <c r="N82" t="s">
+      <c r="O85" t="s">
         <v>144</v>
       </c>
-      <c r="O82" t="s">
+      <c r="P85" t="s">
         <v>144</v>
       </c>
-      <c r="P82" t="s">
+      <c r="Q85" t="s">
         <v>144</v>
       </c>
-      <c r="Q82" t="s">
+      <c r="R85" t="s">
         <v>144</v>
       </c>
-      <c r="T82">
-        <f>INDEX(T24:T81,MATCH(Table2[[#This Row],[Alternative Module Code]],A24:A81,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U82">
+      <c r="U85">
+        <f>INDEX(U24:U84,MATCH(Table2[[#This Row],[Alternative Module Code]],A24:A84,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V85">
         <v>70</v>
       </c>
-      <c r="V82">
+      <c r="W85">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W82">
+      <c r="X85">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
-      <c r="A83" s="3" t="s">
+    <row r="86" spans="1:24">
+      <c r="A86" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B86" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D83" s="28" t="s">
+      <c r="D86" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F86" s="4">
         <v>7</v>
       </c>
-      <c r="G83" s="2">
+      <c r="G86" s="2">
         <v>10</v>
       </c>
-      <c r="H83" s="2"/>
-      <c r="M83" t="s">
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="N86" t="s">
         <v>144</v>
       </c>
-      <c r="N83" t="s">
+      <c r="O86" t="s">
         <v>144</v>
       </c>
-      <c r="O83" t="s">
+      <c r="P86" t="s">
         <v>144</v>
       </c>
-      <c r="P83" t="s">
+      <c r="Q86" t="s">
         <v>144</v>
       </c>
-      <c r="Q83" t="s">
+      <c r="R86" t="s">
         <v>144</v>
       </c>
-      <c r="R83" t="s">
+      <c r="S86" t="s">
         <v>144</v>
       </c>
-      <c r="T83">
-        <f>INDEX(T25:T82,MATCH(Table2[[#This Row],[Alternative Module Code]],A25:A82,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U83">
+      <c r="U86">
+        <f>INDEX(U25:U85,MATCH(Table2[[#This Row],[Alternative Module Code]],A25:A85,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V86">
         <v>40</v>
       </c>
-      <c r="V83">
+      <c r="W86">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>60</v>
       </c>
-      <c r="W83">
+      <c r="X86">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
-      <c r="A84" s="3" t="s">
+    <row r="87" spans="1:24">
+      <c r="A87" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B87" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D84" s="28" t="s">
+      <c r="D87" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E87" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F87" s="4">
         <v>7</v>
       </c>
-      <c r="G84" s="2">
+      <c r="G87" s="2">
         <v>10</v>
       </c>
-      <c r="H84" s="2"/>
-      <c r="M84" t="s">
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="N87" t="s">
         <v>144</v>
       </c>
-      <c r="O84" t="s">
+      <c r="P87" t="s">
         <v>144</v>
       </c>
-      <c r="Q84" t="s">
+      <c r="R87" t="s">
         <v>144</v>
       </c>
-      <c r="T84">
-        <f>INDEX(T26:T83,MATCH(Table2[[#This Row],[Alternative Module Code]],A26:A83,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U84">
+      <c r="U87">
+        <f>INDEX(U26:U86,MATCH(Table2[[#This Row],[Alternative Module Code]],A26:A86,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V87">
         <v>80</v>
       </c>
-      <c r="V84">
+      <c r="W87">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W84">
+      <c r="X87">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:23">
-      <c r="A85" s="3" t="s">
+    <row r="88" spans="1:24">
+      <c r="A88" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B88" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D85" s="28" t="s">
+      <c r="D88" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F88" s="4">
         <v>7</v>
       </c>
-      <c r="G85" s="2">
+      <c r="G88" s="2">
         <v>10</v>
       </c>
-      <c r="H85" s="2"/>
-      <c r="M85" t="s">
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="N88" t="s">
         <v>144</v>
       </c>
-      <c r="N85" t="s">
+      <c r="O88" t="s">
         <v>144</v>
       </c>
-      <c r="O85" t="s">
+      <c r="P88" t="s">
         <v>144</v>
       </c>
-      <c r="P85" t="s">
+      <c r="Q88" t="s">
         <v>144</v>
       </c>
-      <c r="Q85" t="s">
+      <c r="R88" t="s">
         <v>144</v>
       </c>
-      <c r="T85">
-        <f>INDEX(T27:T84,MATCH(Table2[[#This Row],[Alternative Module Code]],A27:A84,0))</f>
+      <c r="U88">
+        <f>INDEX(U27:U87,MATCH(Table2[[#This Row],[Alternative Module Code]],A27:A87,0))</f>
         <v>3</v>
       </c>
-      <c r="U85">
+      <c r="V88">
         <v>0</v>
       </c>
-      <c r="V85">
+      <c r="W88">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W85">
+      <c r="X88">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="1:23">
-      <c r="A86" s="3" t="s">
+    <row r="89" spans="1:24">
+      <c r="A89" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B89" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D86" s="28" t="s">
+      <c r="D89" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F89" s="4">
         <v>7</v>
       </c>
-      <c r="G86" s="2">
+      <c r="G89" s="2">
         <v>10</v>
       </c>
-      <c r="H86" s="2"/>
-      <c r="M86" t="s">
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="N89" t="s">
         <v>144</v>
       </c>
-      <c r="N86" t="s">
+      <c r="O89" t="s">
         <v>144</v>
       </c>
-      <c r="O86" t="s">
+      <c r="P89" t="s">
         <v>144</v>
       </c>
-      <c r="P86" t="s">
+      <c r="Q89" t="s">
         <v>144</v>
       </c>
-      <c r="T86">
-        <f>INDEX(T28:T85,MATCH(Table2[[#This Row],[Alternative Module Code]],A28:A85,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U86">
+      <c r="U89">
+        <f>INDEX(U28:U88,MATCH(Table2[[#This Row],[Alternative Module Code]],A28:A88,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V89">
         <v>70</v>
       </c>
-      <c r="V86">
+      <c r="W89">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W86">
+      <c r="X89">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:23">
-      <c r="A87" s="3" t="s">
+    <row r="90" spans="1:24">
+      <c r="A90" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B90" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D87" s="28" t="s">
+      <c r="D90" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F90" s="4">
         <v>7</v>
       </c>
-      <c r="G87" s="2">
+      <c r="G90" s="2">
         <v>10</v>
       </c>
-      <c r="H87" s="2"/>
-      <c r="M87" t="s">
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="N90" t="s">
         <v>144</v>
       </c>
-      <c r="R87" t="s">
+      <c r="S90" t="s">
         <v>143</v>
       </c>
-      <c r="S87" t="s">
+      <c r="T90" t="s">
         <v>143</v>
       </c>
-      <c r="T87">
-        <f>INDEX(T29:T86,MATCH(Table2[[#This Row],[Alternative Module Code]],A29:A86,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U87">
+      <c r="U90">
+        <f>INDEX(U29:U89,MATCH(Table2[[#This Row],[Alternative Module Code]],A29:A89,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V90">
         <v>50</v>
       </c>
-      <c r="V87">
+      <c r="W90">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W87">
+      <c r="X90">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:23">
-      <c r="A88" s="3" t="s">
+    <row r="91" spans="1:24">
+      <c r="A91" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B91" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D88" s="28" t="s">
+      <c r="D91" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E91" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F91" s="4">
         <v>7</v>
       </c>
-      <c r="G88" s="2">
+      <c r="G91" s="2">
         <v>10</v>
       </c>
-      <c r="H88" s="2"/>
-      <c r="M88" t="s">
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="N91" t="s">
         <v>144</v>
       </c>
-      <c r="O88" t="s">
+      <c r="P91" t="s">
         <v>144</v>
       </c>
-      <c r="Q88" t="s">
+      <c r="R91" t="s">
         <v>144</v>
       </c>
-      <c r="T88">
-        <f>INDEX(T30:T87,MATCH(Table2[[#This Row],[Alternative Module Code]],A30:A87,0))</f>
+      <c r="U91">
+        <f>INDEX(U30:U90,MATCH(Table2[[#This Row],[Alternative Module Code]],A30:A90,0))</f>
         <v>3</v>
       </c>
-      <c r="U88">
+      <c r="V91">
         <v>60</v>
       </c>
-      <c r="V88">
+      <c r="W91">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W88">
+      <c r="X91">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="89" spans="1:23">
-      <c r="A89" s="3" t="s">
+    <row r="92" spans="1:24">
+      <c r="A92" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B92" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D89" s="28" t="s">
+      <c r="D92" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F92" s="4">
         <v>7</v>
       </c>
-      <c r="G89" s="2">
+      <c r="G92" s="2">
         <v>10</v>
       </c>
-      <c r="H89" s="2"/>
-      <c r="M89" t="s">
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="N92" t="s">
         <v>144</v>
       </c>
-      <c r="N89" t="s">
+      <c r="O92" t="s">
         <v>144</v>
       </c>
-      <c r="O89" t="s">
+      <c r="P92" t="s">
         <v>144</v>
       </c>
-      <c r="P89" t="s">
+      <c r="Q92" t="s">
         <v>144</v>
       </c>
-      <c r="Q89" t="s">
+      <c r="R92" t="s">
         <v>144</v>
       </c>
-      <c r="T89">
-        <f>INDEX(T31:T88,MATCH(Table2[[#This Row],[Alternative Module Code]],A31:A88,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U89">
+      <c r="U92">
+        <f>INDEX(U31:U91,MATCH(Table2[[#This Row],[Alternative Module Code]],A31:A91,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V92">
         <v>0</v>
       </c>
-      <c r="V89">
+      <c r="W92">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W89">
+      <c r="X92">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
-      <c r="A90" s="3" t="s">
+    <row r="93" spans="1:24">
+      <c r="A93" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B93" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D90" s="28" t="s">
+      <c r="D93" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E93" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F93" s="4">
         <v>7</v>
       </c>
-      <c r="G90" s="28">
+      <c r="G93" s="28">
         <v>10</v>
       </c>
-      <c r="H90" s="28"/>
-      <c r="M90" t="s">
+      <c r="H93" s="28"/>
+      <c r="I93" s="28"/>
+      <c r="N93" t="s">
         <v>144</v>
       </c>
-      <c r="N90" t="s">
+      <c r="O93" t="s">
         <v>144</v>
       </c>
-      <c r="O90" t="s">
+      <c r="P93" t="s">
         <v>144</v>
       </c>
-      <c r="P90" t="s">
+      <c r="Q93" t="s">
         <v>144</v>
       </c>
-      <c r="Q90" t="s">
+      <c r="R93" t="s">
         <v>144</v>
       </c>
-      <c r="T90">
-        <f>INDEX(T32:T89,MATCH(Table2[[#This Row],[Alternative Module Code]],A32:A89,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U90">
+      <c r="U93">
+        <f>INDEX(U32:U92,MATCH(Table2[[#This Row],[Alternative Module Code]],A32:A92,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V93">
         <v>50</v>
       </c>
-      <c r="V90">
+      <c r="W93">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W90">
+      <c r="X93">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
-      <c r="A91" s="3" t="s">
+    <row r="94" spans="1:24">
+      <c r="A94" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B94" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F91" s="4">
-        <v>7</v>
-      </c>
-      <c r="G91" s="28">
-        <v>10</v>
-      </c>
-      <c r="H91" s="28"/>
-      <c r="M91" t="s">
-        <v>144</v>
-      </c>
-      <c r="R91" t="s">
-        <v>144</v>
-      </c>
-      <c r="S91" t="s">
-        <v>144</v>
-      </c>
-      <c r="T91">
-        <v>2</v>
-      </c>
-      <c r="U91">
-        <v>0</v>
-      </c>
-      <c r="V91">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W91">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23">
-      <c r="A92" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C92" s="3"/>
-      <c r="D92" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F92" s="4">
-        <v>7</v>
-      </c>
-      <c r="G92" s="28">
-        <v>10</v>
-      </c>
-      <c r="H92" s="28"/>
-      <c r="M92" t="s">
-        <v>144</v>
-      </c>
-      <c r="N92" t="s">
-        <v>144</v>
-      </c>
-      <c r="R92" t="s">
-        <v>144</v>
-      </c>
-      <c r="S92" t="s">
-        <v>144</v>
-      </c>
-      <c r="T92">
-        <v>2</v>
-      </c>
-      <c r="U92">
-        <v>0</v>
-      </c>
-      <c r="V92">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W92">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23">
-      <c r="A93" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F93" s="4">
-        <v>7</v>
-      </c>
-      <c r="G93" s="28">
-        <v>10</v>
-      </c>
-      <c r="H93" s="28"/>
-      <c r="M93" t="s">
-        <v>144</v>
-      </c>
-      <c r="R93" t="s">
-        <v>144</v>
-      </c>
-      <c r="S93" t="s">
-        <v>144</v>
-      </c>
-      <c r="T93">
-        <v>2</v>
-      </c>
-      <c r="U93">
-        <v>0</v>
-      </c>
-      <c r="V93">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W93">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23">
-      <c r="A94" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="28" t="s">
@@ -35599,116 +35896,97 @@
       <c r="F94" s="4">
         <v>7</v>
       </c>
-      <c r="G94" s="2">
-        <v>20</v>
-      </c>
-      <c r="H94" s="2"/>
-      <c r="M94" t="s">
-        <v>143</v>
-      </c>
+      <c r="G94" s="28">
+        <v>10</v>
+      </c>
+      <c r="H94" s="28"/>
+      <c r="I94" s="28"/>
       <c r="N94" t="s">
-        <v>143</v>
-      </c>
-      <c r="O94" t="s">
-        <v>143</v>
-      </c>
-      <c r="P94" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>143</v>
-      </c>
-      <c r="R94" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S94" t="s">
-        <v>143</v>
-      </c>
-      <c r="T94">
-        <v>3</v>
+        <v>144</v>
+      </c>
+      <c r="T94" t="s">
+        <v>144</v>
       </c>
       <c r="U94">
+        <v>2</v>
+      </c>
+      <c r="V94">
         <v>0</v>
       </c>
-      <c r="V94">
+      <c r="W94">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W94">
+      <c r="X94">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:23">
+    <row r="95" spans="1:24">
       <c r="A95" s="3" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F95" s="4">
         <v>7</v>
       </c>
-      <c r="G95" s="2">
-        <v>20</v>
-      </c>
-      <c r="H95" s="2"/>
-      <c r="M95" t="s">
-        <v>143</v>
-      </c>
+      <c r="G95" s="28">
+        <v>10</v>
+      </c>
+      <c r="H95" s="28"/>
+      <c r="I95" s="28"/>
       <c r="N95" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O95" t="s">
-        <v>143</v>
-      </c>
-      <c r="P95" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>143</v>
-      </c>
-      <c r="R95" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S95" t="s">
-        <v>143</v>
-      </c>
-      <c r="T95">
-        <v>4</v>
+        <v>144</v>
+      </c>
+      <c r="T95" t="s">
+        <v>144</v>
       </c>
       <c r="U95">
+        <v>2</v>
+      </c>
+      <c r="V95">
         <v>0</v>
       </c>
-      <c r="V95">
+      <c r="W95">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W95">
+      <c r="X95">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:23">
+    <row r="96" spans="1:24">
       <c r="A96" s="3" t="s">
-        <v>313</v>
+        <v>246</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F96" s="4">
         <v>7</v>
@@ -35717,81 +35995,95 @@
         <v>10</v>
       </c>
       <c r="H96" s="28"/>
-      <c r="M96" t="s">
-        <v>144</v>
-      </c>
-      <c r="R96" t="s">
+      <c r="I96" s="28"/>
+      <c r="N96" t="s">
         <v>144</v>
       </c>
       <c r="S96" t="s">
         <v>144</v>
       </c>
-      <c r="T96">
-        <v>2</v>
+      <c r="T96" t="s">
+        <v>144</v>
       </c>
       <c r="U96">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W96">
+        <v>100</v>
+      </c>
+      <c r="X96">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30.000000000000004</v>
-      </c>
-    </row>
-    <row r="97" spans="1:23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24">
       <c r="A97" s="3" t="s">
-        <v>373</v>
+        <v>181</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>374</v>
+        <v>184</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F97" s="4">
         <v>7</v>
       </c>
-      <c r="G97" s="28">
-        <v>10</v>
-      </c>
-      <c r="H97" s="28"/>
-      <c r="M97" t="s">
-        <v>144</v>
+      <c r="G97" s="2">
+        <v>20</v>
+      </c>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="N97" t="s">
+        <v>143</v>
+      </c>
+      <c r="O97" t="s">
+        <v>143</v>
+      </c>
+      <c r="P97" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>143</v>
       </c>
       <c r="R97" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S97" t="s">
-        <v>144</v>
-      </c>
-      <c r="T97">
-        <v>2</v>
+        <v>143</v>
+      </c>
+      <c r="T97" t="s">
+        <v>143</v>
       </c>
       <c r="U97">
+        <v>3</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="V97">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>0</v>
-      </c>
-      <c r="W97">
+      <c r="X97">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24">
       <c r="A98" s="3" t="s">
-        <v>318</v>
+        <v>182</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>319</v>
+        <v>185</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="28" t="s">
@@ -35803,215 +36095,464 @@
       <c r="F98" s="4">
         <v>7</v>
       </c>
-      <c r="G98" s="28">
-        <v>10</v>
-      </c>
-      <c r="H98" s="28"/>
-      <c r="M98" t="s">
-        <v>144</v>
+      <c r="G98" s="2">
+        <v>20</v>
+      </c>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="N98" t="s">
+        <v>143</v>
+      </c>
+      <c r="O98" t="s">
+        <v>143</v>
+      </c>
+      <c r="P98" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>143</v>
       </c>
       <c r="R98" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S98" t="s">
-        <v>144</v>
-      </c>
-      <c r="T98">
-        <v>2</v>
+        <v>143</v>
+      </c>
+      <c r="T98" t="s">
+        <v>143</v>
       </c>
       <c r="U98">
+        <v>4</v>
+      </c>
+      <c r="V98">
         <v>0</v>
       </c>
-      <c r="V98">
+      <c r="W98">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W98">
+      <c r="X98">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:24">
       <c r="A99" s="3" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F99" s="4">
         <v>7</v>
       </c>
       <c r="G99" s="28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H99" s="28"/>
-      <c r="M99" t="s">
+      <c r="I99" s="28"/>
+      <c r="N99" t="s">
         <v>144</v>
       </c>
-      <c r="P99" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>143</v>
-      </c>
-      <c r="T99">
-        <v>4</v>
+      <c r="S99" t="s">
+        <v>144</v>
+      </c>
+      <c r="T99" t="s">
+        <v>144</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V99">
+        <v>70</v>
+      </c>
+      <c r="W99">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W99">
+        <v>30</v>
+      </c>
+      <c r="X99">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" spans="1:23">
+        <v>30.000000000000004</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24">
       <c r="A100" s="3" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F100" s="4">
         <v>7</v>
       </c>
       <c r="G100" s="28">
+        <v>10</v>
+      </c>
+      <c r="H100" s="28"/>
+      <c r="I100" s="28"/>
+      <c r="N100" t="s">
+        <v>144</v>
+      </c>
+      <c r="S100" t="s">
+        <v>144</v>
+      </c>
+      <c r="T100" t="s">
+        <v>144</v>
+      </c>
+      <c r="U100">
+        <v>2</v>
+      </c>
+      <c r="V100">
+        <v>100</v>
+      </c>
+      <c r="W100">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>0</v>
+      </c>
+      <c r="X100">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24">
+      <c r="A101" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F101" s="4">
+        <v>7</v>
+      </c>
+      <c r="G101" s="28">
+        <v>10</v>
+      </c>
+      <c r="H101" s="28"/>
+      <c r="I101" s="28"/>
+      <c r="N101" t="s">
+        <v>144</v>
+      </c>
+      <c r="S101" t="s">
+        <v>144</v>
+      </c>
+      <c r="T101" t="s">
+        <v>144</v>
+      </c>
+      <c r="U101">
+        <v>2</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X101">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24">
+      <c r="A102" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F102" s="4">
+        <v>7</v>
+      </c>
+      <c r="G102" s="28">
         <v>20</v>
       </c>
-      <c r="H100" s="28"/>
-      <c r="M100" t="s">
+      <c r="H102" s="28"/>
+      <c r="I102" s="28"/>
+      <c r="N102" t="s">
         <v>144</v>
       </c>
-      <c r="P100" t="s">
+      <c r="Q102" t="s">
         <v>143</v>
       </c>
-      <c r="Q100" t="s">
+      <c r="R102" t="s">
         <v>143</v>
       </c>
-      <c r="T100">
+      <c r="U102">
         <v>4</v>
       </c>
-      <c r="U100">
+      <c r="V102">
+        <v>0</v>
+      </c>
+      <c r="W102">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X102">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24">
+      <c r="A103" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F103" s="4">
+        <v>7</v>
+      </c>
+      <c r="G103" s="28">
+        <v>20</v>
+      </c>
+      <c r="H103" s="28"/>
+      <c r="I103" s="28"/>
+      <c r="N103" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>143</v>
+      </c>
+      <c r="R103" t="s">
+        <v>143</v>
+      </c>
+      <c r="U103">
+        <v>4</v>
+      </c>
+      <c r="V103">
         <v>50</v>
       </c>
-      <c r="V100">
+      <c r="W103">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W100">
+      <c r="X103">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
-      <c r="A101"/>
-      <c r="B101"/>
-      <c r="C101"/>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
-    </row>
-    <row r="102" spans="1:23">
-      <c r="A102"/>
-      <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-    </row>
-    <row r="103" spans="1:23">
-      <c r="A103"/>
-      <c r="B103"/>
-      <c r="C103"/>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103"/>
-    </row>
-    <row r="104" spans="1:23">
-      <c r="A104"/>
-      <c r="B104"/>
-      <c r="C104"/>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
-    </row>
-    <row r="105" spans="1:23">
-      <c r="A105"/>
-      <c r="B105"/>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
-    </row>
-    <row r="106" spans="1:23">
-      <c r="A106"/>
-      <c r="B106"/>
-      <c r="C106"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
-    </row>
-    <row r="107" spans="1:23">
-      <c r="A107"/>
-      <c r="B107"/>
-      <c r="C107"/>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
-    </row>
-    <row r="108" spans="1:23">
-      <c r="A108"/>
-      <c r="B108"/>
-      <c r="C108"/>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
-    </row>
-    <row r="109" spans="1:23">
-      <c r="A109"/>
-      <c r="B109"/>
-      <c r="C109"/>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
-    </row>
-    <row r="110" spans="1:23">
+    <row r="104" spans="1:24">
+      <c r="A104" s="54" t="s">
+        <v>404</v>
+      </c>
+      <c r="B104" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="C104" s="54"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="56"/>
+      <c r="H104" s="28"/>
+      <c r="I104" s="28"/>
+      <c r="J104" s="57"/>
+      <c r="L104" s="57"/>
+      <c r="M104" s="57"/>
+      <c r="O104" s="57"/>
+      <c r="P104" s="57"/>
+      <c r="Q104" s="57"/>
+      <c r="R104" s="57"/>
+      <c r="V104" s="57"/>
+      <c r="W104" s="58">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X104" s="58">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24">
+      <c r="A105" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="B105" s="54" t="s">
+        <v>407</v>
+      </c>
+      <c r="C105" s="54"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="56"/>
+      <c r="H105" s="28"/>
+      <c r="I105" s="28"/>
+      <c r="J105" s="57"/>
+      <c r="L105" s="57"/>
+      <c r="M105" s="57"/>
+      <c r="O105" s="57"/>
+      <c r="P105" s="57"/>
+      <c r="Q105" s="57"/>
+      <c r="R105" s="57"/>
+      <c r="V105" s="57"/>
+      <c r="W105" s="58">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X105" s="58">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24">
+      <c r="A106" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="B106" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="C106" s="54"/>
+      <c r="D106" s="28"/>
+      <c r="E106" s="54"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="56"/>
+      <c r="H106" s="28"/>
+      <c r="I106" s="28"/>
+      <c r="J106" s="57"/>
+      <c r="L106" s="57"/>
+      <c r="M106" s="57"/>
+      <c r="O106" s="57"/>
+      <c r="P106" s="57"/>
+      <c r="Q106" s="57"/>
+      <c r="R106" s="57"/>
+      <c r="V106" s="57"/>
+      <c r="W106" s="58">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X106" s="58">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24">
+      <c r="A107" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="B107" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="C107" s="54"/>
+      <c r="D107" s="28"/>
+      <c r="E107" s="54"/>
+      <c r="F107" s="55"/>
+      <c r="G107" s="56"/>
+      <c r="H107" s="28"/>
+      <c r="I107" s="28"/>
+      <c r="J107" s="57"/>
+      <c r="L107" s="57"/>
+      <c r="M107" s="57"/>
+      <c r="O107" s="57"/>
+      <c r="P107" s="57"/>
+      <c r="Q107" s="57"/>
+      <c r="R107" s="57"/>
+      <c r="V107" s="57"/>
+      <c r="W107" s="58">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X107" s="58">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24">
+      <c r="A108" s="54" t="s">
+        <v>412</v>
+      </c>
+      <c r="B108" s="54" t="s">
+        <v>413</v>
+      </c>
+      <c r="C108" s="54"/>
+      <c r="D108" s="28"/>
+      <c r="E108" s="54"/>
+      <c r="F108" s="55"/>
+      <c r="G108" s="56"/>
+      <c r="H108" s="28"/>
+      <c r="I108" s="28"/>
+      <c r="J108" s="57"/>
+      <c r="L108" s="57"/>
+      <c r="M108" s="57"/>
+      <c r="O108" s="57"/>
+      <c r="P108" s="57"/>
+      <c r="Q108" s="57"/>
+      <c r="R108" s="57"/>
+      <c r="V108" s="57"/>
+      <c r="W108" s="58">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X108" s="58">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24">
+      <c r="A109" s="54" t="s">
+        <v>414</v>
+      </c>
+      <c r="B109" s="54" t="s">
+        <v>415</v>
+      </c>
+      <c r="C109" s="54"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="54"/>
+      <c r="F109" s="55"/>
+      <c r="G109" s="56"/>
+      <c r="H109" s="28"/>
+      <c r="I109" s="28"/>
+      <c r="J109" s="57"/>
+      <c r="L109" s="57"/>
+      <c r="M109" s="57"/>
+      <c r="O109" s="57"/>
+      <c r="P109" s="57"/>
+      <c r="Q109" s="57"/>
+      <c r="R109" s="57"/>
+      <c r="V109" s="57"/>
+      <c r="W109" s="58">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X109" s="58">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24">
       <c r="A110"/>
       <c r="B110"/>
       <c r="C110"/>
@@ -36020,8 +36561,9 @@
       <c r="F110"/>
       <c r="G110"/>
       <c r="H110"/>
-    </row>
-    <row r="111" spans="1:23">
+      <c r="I110"/>
+    </row>
+    <row r="111" spans="1:24">
       <c r="A111"/>
       <c r="B111"/>
       <c r="C111"/>
@@ -36030,8 +36572,9 @@
       <c r="F111"/>
       <c r="G111"/>
       <c r="H111"/>
-    </row>
-    <row r="112" spans="1:23">
+      <c r="I111"/>
+    </row>
+    <row r="112" spans="1:24">
       <c r="A112"/>
       <c r="B112"/>
       <c r="C112"/>
@@ -36040,6 +36583,7 @@
       <c r="F112"/>
       <c r="G112"/>
       <c r="H112"/>
+      <c r="I112"/>
     </row>
     <row r="113" customFormat="1"/>
     <row r="114" customFormat="1"/>
@@ -36057,42 +36601,76 @@
     <row r="126" customFormat="1"/>
     <row r="127" customFormat="1"/>
     <row r="128" customFormat="1"/>
-    <row r="129" spans="1:8">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
+    <row r="129" spans="1:9">
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129"/>
+      <c r="I129"/>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="I131"/>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E100">
-    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="SEMD">
+  <conditionalFormatting sqref="E2:E109">
+    <cfRule type="containsText" dxfId="27" priority="19" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="26" priority="20" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="14" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="25" priority="21" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E96:E100">
-    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="SEMD">
-      <formula>NOT(ISERROR(SEARCH("SEMD",E96)))</formula>
+  <conditionalFormatting sqref="E99:E103">
+    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="SEMD">
+      <formula>NOT(ISERROR(SEARCH("SEMD",E99)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="SEM2">
-      <formula>NOT(ISERROR(SEARCH("SEM2",E96)))</formula>
+    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="SEM2">
+      <formula>NOT(ISERROR(SEARCH("SEM2",E99)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="SEM1">
-      <formula>NOT(ISERROR(SEARCH("SEM1",E96)))</formula>
+    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="SEM1">
+      <formula>NOT(ISERROR(SEARCH("SEM1",E99)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F100">
-    <cfRule type="colorScale" priority="161">
+  <conditionalFormatting sqref="F2:F109">
+    <cfRule type="colorScale" priority="168">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -36101,8 +36679,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F100">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="F99:F103">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -36111,8 +36689,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
-    <cfRule type="colorScale" priority="163">
+  <conditionalFormatting sqref="G2:H109">
+    <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="num" val="10"/>
         <cfvo type="percentile" val="50"/>
@@ -36123,8 +36701,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G96:G100">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="G99:H103">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="10"/>
         <cfvo type="percentile" val="50"/>
@@ -36135,25 +36713,33 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:T95 H96:S100">
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="O">
-      <formula>NOT(ISERROR(SEARCH("O",H2)))</formula>
+  <conditionalFormatting sqref="N99:T103 N2:U98">
+    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="O">
+      <formula>NOT(ISERROR(SEARCH("O",N2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="C">
-      <formula>NOT(ISERROR(SEARCH("C",H2)))</formula>
+    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="C">
+      <formula>NOT(ISERROR(SEARCH("C",N2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T96:T100">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="O">
-      <formula>NOT(ISERROR(SEARCH("O",T96)))</formula>
+  <conditionalFormatting sqref="U99:U103">
+    <cfRule type="containsText" dxfId="17" priority="9" operator="containsText" text="O">
+      <formula>NOT(ISERROR(SEARCH("O",U99)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="C">
-      <formula>NOT(ISERROR(SEARCH("C",T96)))</formula>
+    <cfRule type="containsText" dxfId="16" priority="10" operator="containsText" text="C">
+      <formula>NOT(ISERROR(SEARCH("C",U99)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W100">
-    <cfRule type="expression" dxfId="0" priority="9">
-      <formula>W2&lt;&gt;V2</formula>
+  <conditionalFormatting sqref="X2:X109">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>X2&lt;&gt;W2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:M109">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="O">
+      <formula>NOT(ISERROR(SEARCH("O",I2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="C">
+      <formula>NOT(ISERROR(SEARCH("C",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36165,8 +36751,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{AB48118A-1CFE-488B-B12E-453EA0CADD16}">
-            <xm:f>NOT(ISERROR(SEARCH("-",I2)))</xm:f>
+          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{AB48118A-1CFE-488B-B12E-453EA0CADD16}">
+            <xm:f>NOT(ISERROR(SEARCH("-",N2)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
               <fill>
@@ -36176,11 +36762,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:T95 I96:S100</xm:sqref>
+          <xm:sqref>N2:U98 N99:T103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{631B2A6D-16EC-488F-9A76-B8FF0576AF03}">
-            <xm:f>NOT(ISERROR(SEARCH("-",T96)))</xm:f>
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{631B2A6D-16EC-488F-9A76-B8FF0576AF03}">
+            <xm:f>NOT(ISERROR(SEARCH("-",U99)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
               <fill>
@@ -36190,7 +36776,21 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>T96:T100</xm:sqref>
+          <xm:sqref>U99:U103</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{611DB1DB-AE5D-4557-A9D5-505B18ADA866}">
+            <xm:f>NOT(ISERROR(SEARCH("-",J2)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-0.24994659260841701"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J2:M109</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -36201,11 +36801,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4F541C-C22C-46EF-BD21-4F8C93ABA5A9}">
   <dimension ref="A3:F70"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.54296875" customWidth="1"/>
+    <col min="1" max="1" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6">
